--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15081,4 +15082,842 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6987.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2318.4375</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11169.71</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0D672NXC8</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6987.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2318.4375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11169.71</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6987.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2318.4375</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11169.71</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6987.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2318.4375</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11169.71</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14585</v>
+      </c>
+      <c r="E6" t="n">
+        <v>574</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6126.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19231.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17523</v>
+      </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1107.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4022.030000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0FPGDVVCX</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>17523</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1107.58</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4022.030000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2656</v>
+      </c>
+      <c r="E9" t="n">
+        <v>82</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2457.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4966.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8117</v>
+      </c>
+      <c r="E10" t="n">
+        <v>310</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1298.11202</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51813.53</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>991</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F11" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3047.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="F12" t="n">
+        <v>445.1225</v>
+      </c>
+      <c r="G12" t="n">
+        <v>63.3475</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0D672NXC8</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3047.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>445.1225</v>
+      </c>
+      <c r="G13" t="n">
+        <v>63.3475</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3047.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>445.1225</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63.3475</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3047.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="F15" t="n">
+        <v>445.1225</v>
+      </c>
+      <c r="G15" t="n">
+        <v>63.3475</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3363.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>201.318</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DCK56Q85</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3363.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>201.318</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DDC3GVZW</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3363.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>201.318</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3363.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>201.318</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DKJZDY72</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3363.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>201.318</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TG B0CDPP45BM Steam Cleaner 300 ml</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10413</v>
+      </c>
+      <c r="E21" t="n">
+        <v>165</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3940.71</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11946.61</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TG B0DNJS23HS  10 in 1 Steam Cleaner</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12160</v>
+      </c>
+      <c r="E22" t="n">
+        <v>401</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6984.82</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14521.19</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -15090,7 +15090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15157,19 +15157,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6987.5</v>
+        <v>9316.666666666666</v>
       </c>
       <c r="E2" t="n">
-        <v>76.25</v>
+        <v>101.6666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>2318.4375</v>
+        <v>3091.25</v>
       </c>
       <c r="G2" t="n">
-        <v>11169.71</v>
+        <v>14892.94666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -15190,23 +15190,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6987.5</v>
+        <v>9316.666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>76.25</v>
+        <v>101.6666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>2318.4375</v>
+        <v>3091.25</v>
       </c>
       <c r="G3" t="n">
-        <v>11169.71</v>
+        <v>14892.94666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -15227,23 +15227,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6987.5</v>
+        <v>9316.666666666666</v>
       </c>
       <c r="E4" t="n">
-        <v>76.25</v>
+        <v>101.6666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>2318.4375</v>
+        <v>3091.25</v>
       </c>
       <c r="G4" t="n">
-        <v>11169.71</v>
+        <v>14892.94666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -15259,28 +15259,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6987.5</v>
+        <v>7292.5</v>
       </c>
       <c r="E5" t="n">
-        <v>76.25</v>
+        <v>287</v>
       </c>
       <c r="F5" t="n">
-        <v>2318.4375</v>
+        <v>3063.13</v>
       </c>
       <c r="G5" t="n">
-        <v>11169.71</v>
+        <v>9615.715</v>
       </c>
       <c r="H5" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -15301,23 +15301,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14585</v>
+        <v>7292.5</v>
       </c>
       <c r="E6" t="n">
-        <v>574</v>
+        <v>287</v>
       </c>
       <c r="F6" t="n">
-        <v>6126.26</v>
+        <v>3063.13</v>
       </c>
       <c r="G6" t="n">
-        <v>19231.43</v>
+        <v>9615.715</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -15342,19 +15342,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17523</v>
+        <v>11682</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>1107.58</v>
+        <v>738.3866666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>4022.030000000001</v>
+        <v>2681.353333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -15375,23 +15375,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17523</v>
+        <v>11682</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F8" t="n">
-        <v>1107.58</v>
+        <v>738.3866666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>4022.030000000001</v>
+        <v>2681.353333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -15407,28 +15407,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2656</v>
+        <v>11682</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>2457.8</v>
+        <v>738.3866666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>4966.95</v>
+        <v>2681.353333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -15444,28 +15444,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8117</v>
+        <v>7162</v>
       </c>
       <c r="E10" t="n">
-        <v>310</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>1298.11202</v>
+        <v>662.2533333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>51813.53</v>
+        <v>348.89</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -15481,28 +15481,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>991</v>
+        <v>7162</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="F11" t="n">
-        <v>368.28</v>
+        <v>662.2533333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>348.89</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -15518,28 +15518,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3047.5</v>
+        <v>7162</v>
       </c>
       <c r="E12" t="n">
-        <v>27.25</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>445.1225</v>
+        <v>662.2533333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>63.3475</v>
+        <v>348.89</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -15555,28 +15555,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3047.5</v>
+        <v>1328</v>
       </c>
       <c r="E13" t="n">
-        <v>27.25</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>445.1225</v>
+        <v>1228.9</v>
       </c>
       <c r="G13" t="n">
-        <v>63.3475</v>
+        <v>2483.475</v>
       </c>
       <c r="H13" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -15592,28 +15592,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3047.5</v>
+        <v>1328</v>
       </c>
       <c r="E14" t="n">
-        <v>27.25</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>445.1225</v>
+        <v>1228.9</v>
       </c>
       <c r="G14" t="n">
-        <v>63.3475</v>
+        <v>2483.475</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -15629,28 +15629,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3047.5</v>
+        <v>8117</v>
       </c>
       <c r="E15" t="n">
-        <v>27.25</v>
+        <v>310</v>
       </c>
       <c r="F15" t="n">
-        <v>445.1225</v>
+        <v>1298.11202</v>
       </c>
       <c r="G15" t="n">
-        <v>63.3475</v>
+        <v>51813.53</v>
       </c>
       <c r="H15" t="n">
-        <v>0.25</v>
+        <v>16</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -15666,22 +15666,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3363.4</v>
+        <v>495.5</v>
       </c>
       <c r="E16" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="F16" t="n">
-        <v>201.318</v>
+        <v>184.14</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -15703,22 +15703,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3363.4</v>
+        <v>495.5</v>
       </c>
       <c r="E17" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="F17" t="n">
-        <v>201.318</v>
+        <v>184.14</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -15740,28 +15740,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3363.4</v>
+        <v>4063.333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>7.8</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>201.318</v>
+        <v>593.4966666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>84.46333333333332</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -15777,28 +15777,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3363.4</v>
+        <v>4063.333333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>7.8</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>201.318</v>
+        <v>593.4966666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>84.46333333333332</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -15814,28 +15814,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DKJZDY72</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3363.4</v>
+        <v>4063.333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>7.8</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>201.318</v>
+        <v>593.4966666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>84.46333333333332</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -15846,33 +15846,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TG B0CDPP45BM Steam Cleaner 300 ml</t>
+          <t>No Portfolio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10413</v>
+        <v>8408.5</v>
       </c>
       <c r="E21" t="n">
-        <v>165</v>
+        <v>19.5</v>
       </c>
       <c r="F21" t="n">
-        <v>3940.71</v>
+        <v>503.295</v>
       </c>
       <c r="G21" t="n">
-        <v>11946.61</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -15883,35 +15883,109 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>No Portfolio</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8408.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>503.295</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TG B0CDPP45BM Steam Cleaner 300 ml</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10413</v>
+      </c>
+      <c r="E23" t="n">
+        <v>165</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3940.71</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11946.61</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TG B0DNJS23HS  10 in 1 Steam Cleaner</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>B0DNJS23HS</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D24" t="n">
         <v>12160</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>401</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>6984.82</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G24" t="n">
         <v>14521.19</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H24" t="n">
         <v>5</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9316.666666666666</v>
+        <v>9317</v>
       </c>
       <c r="E2" t="n">
-        <v>101.6666666666667</v>
+        <v>102</v>
       </c>
       <c r="F2" t="n">
         <v>3091.25</v>
@@ -11566,7 +11566,7 @@
         <v>14892.94666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>4.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9316.666666666666</v>
+        <v>9317</v>
       </c>
       <c r="E3" t="n">
-        <v>101.6666666666667</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
         <v>3091.25</v>
@@ -11603,7 +11603,7 @@
         <v>14892.94666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>4.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -11628,10 +11628,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9316.666666666666</v>
+        <v>9317</v>
       </c>
       <c r="E4" t="n">
-        <v>101.6666666666667</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
         <v>3091.25</v>
@@ -11640,7 +11640,7 @@
         <v>14892.94666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>4.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7292.5</v>
+        <v>7292</v>
       </c>
       <c r="E5" t="n">
         <v>287</v>
@@ -11677,7 +11677,7 @@
         <v>9615.715</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7292.5</v>
+        <v>7292</v>
       </c>
       <c r="E6" t="n">
         <v>287</v>
@@ -11714,7 +11714,7 @@
         <v>9615.715</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>11682</v>
       </c>
       <c r="E7" t="n">
-        <v>53.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
         <v>738.3866666666667</v>
@@ -11779,7 +11779,7 @@
         <v>11682</v>
       </c>
       <c r="E8" t="n">
-        <v>53.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
         <v>738.3866666666667</v>
@@ -11816,7 +11816,7 @@
         <v>11682</v>
       </c>
       <c r="E9" t="n">
-        <v>53.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
         <v>738.3866666666667</v>
@@ -11853,7 +11853,7 @@
         <v>7162</v>
       </c>
       <c r="E10" t="n">
-        <v>34.66666666666666</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
         <v>662.2533333333333</v>
@@ -11862,7 +11862,7 @@
         <v>348.89</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>7162</v>
       </c>
       <c r="E11" t="n">
-        <v>34.66666666666666</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>662.2533333333333</v>
@@ -11899,7 +11899,7 @@
         <v>348.89</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>7162</v>
       </c>
       <c r="E12" t="n">
-        <v>34.66666666666666</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
         <v>662.2533333333333</v>
@@ -11936,7 +11936,7 @@
         <v>348.89</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>2483.475</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>2483.475</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>495.5</v>
+        <v>496</v>
       </c>
       <c r="E16" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
         <v>184.14</v>
@@ -12109,10 +12109,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>495.5</v>
+        <v>496</v>
       </c>
       <c r="E17" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
         <v>184.14</v>
@@ -12146,10 +12146,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4063.333333333333</v>
+        <v>4063</v>
       </c>
       <c r="E18" t="n">
-        <v>36.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="F18" t="n">
         <v>593.4966666666667</v>
@@ -12158,7 +12158,7 @@
         <v>84.46333333333332</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -12183,10 +12183,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4063.333333333333</v>
+        <v>4063</v>
       </c>
       <c r="E19" t="n">
-        <v>36.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
         <v>593.4966666666667</v>
@@ -12195,7 +12195,7 @@
         <v>84.46333333333332</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -12220,10 +12220,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4063.333333333333</v>
+        <v>4063</v>
       </c>
       <c r="E20" t="n">
-        <v>36.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>593.4966666666667</v>
@@ -12232,7 +12232,7 @@
         <v>84.46333333333332</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -12257,10 +12257,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8408.5</v>
+        <v>8408</v>
       </c>
       <c r="E21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
         <v>503.295</v>
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8408.5</v>
+        <v>8408</v>
       </c>
       <c r="E22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>503.295</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,46 +415,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H339"/>
+  <dimension ref="A1:H325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -560,12 +548,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HnK_SP_PT_SPM-01_B0DCK7J87D</t>
+          <t>Nex_HPC_SP_Auto_KM-01_B0DM66B2DW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -588,12 +576,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_Auto_KM-01_B0DM66B2DW</t>
+          <t>Nex_HPC_SP_CT_FS-01_B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -616,12 +604,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_CT_FS-01_B0D9KFZYG8</t>
+          <t>Nex_HPC_SP_CT_V-03_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -644,12 +632,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_CT_V-03_B0DQCWRG3H</t>
+          <t>Nex_HPC_SP_KT_EA-01_B0D67727VG_Exact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -672,12 +660,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_BR-01_B0DKJXRXKM_BCG</t>
+          <t>Nex_HPC_SP_KT_HSB-03_B0D9KFP4MG_MV_Exact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -700,12 +688,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_EA-01_B0D67727VG_Exact</t>
+          <t>Nex_HPC_SP_KT_V-01_CVR_Exact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -728,12 +716,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_HSB-03_B0D9KFP4MG_MV_Exact</t>
+          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_CG_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -756,12 +744,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-01_B0D83Q7L8W_BCG_Phrase_Exact</t>
+          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -784,12 +772,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-01_CVR_Exact</t>
+          <t>Nex_HPC_SP_KT_V-03_Comp_B0DQCWRG3H_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -812,12 +800,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_CG_LV_Phrase &amp; Exact</t>
+          <t>Nex_HPC_SP_PT_CFM-01_B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -840,7 +828,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_MV_Phrase &amp; Exact</t>
+          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -868,12 +856,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_Comp_B0DQCWRG3H_HV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_CT_(SM-01)_Wet &amp; Dry Mops</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -896,12 +884,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_PT_CFM-01_B0DM6BB3VT</t>
+          <t>Nex_HnK_SP_CT_GS-02_B0CDPMX152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -924,12 +912,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
+          <t>Nex_HnK_SP_CT_SC-01_B0CDPP45BM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -952,12 +940,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Auto_MR-01_B0CYSLCRQS</t>
+          <t>Nex_HnK_SP_Comp_PT_GS-02_B0CDPMX152</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -980,7 +968,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_(SM-01)_Wet &amp; Dry Mops</t>
+          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1008,12 +996,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_GS-02_B0CDPMX152</t>
+          <t>Nex_HnK_SP_KT_AP-04_B0GN8N96R5_Gen_Exact_HV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1036,12 +1024,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_SC-01_B0CDPP45BM</t>
+          <t>Nex_HnK_SP_KT_CAP-05_B0GN86G345_Gen_HV_Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1064,7 +1052,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_GS-02_B0CDPMX152</t>
+          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_CG_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1092,12 +1080,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_HU-02_B0DVC8NYY2</t>
+          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_Gen_Phrase_HV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1120,12 +1108,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_SC-01_B0CDPP45BM</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_BCG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1148,12 +1136,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1176,12 +1164,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_AP-04_B0GN8N96R5_Gen_Exact_HV</t>
+          <t>Nex_HnK_SP_KT_LR-02_B0D845B2DG_LV_Exact_Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1204,12 +1192,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_CAP-05_B0GN86G345_Gen_HV_Phrase</t>
+          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1232,12 +1220,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_CG_MV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_CG_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1260,12 +1248,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_Gen_Phrase_HV</t>
+          <t>Nex_HnK_SP_KT_MR-02_B0DCK7ZH5P_Gen_HV_Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1288,12 +1276,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_GS-05_B0D383WQPB_Gen_HV_Phrase</t>
+          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Gen_HV_Exact</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1316,12 +1304,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_BCG</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1344,12 +1332,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1372,12 +1360,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_LR-02_B0D845B2DG_LV_Exact_Phrase</t>
+          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1400,12 +1388,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_CG_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1428,12 +1416,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_CG_LV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1456,12 +1444,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-02_B0DCK7ZH5P_Gen_HV_Phrase</t>
+          <t>Nex_HnK_SP|SS-02-B0DNJP9T35| Auto</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1484,12 +1472,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Adaptive Campaign</t>
+          <t>Nex_Hnk_SP_Auto_CAP-05_B0GN86G345</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1512,12 +1500,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Gen_HV_Exact</t>
+          <t>Nex_Hnk_SP_KT - MC-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1540,12 +1528,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_LV_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SP_KT_ST-02_B0GN94YDY2_CG_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1568,12 +1556,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
+          <t>Nex_Hnk_SP_PT - MC-01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1596,12 +1584,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Phrase</t>
+          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1624,40 +1612,40 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
+          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>501.05</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>16173</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>668.64</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_CG_MV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0CDPMX152 - Handheld Garment Steamer - KT - Comp - Multi Ad Group 07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1680,124 +1668,124 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>8066.38</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>51770</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>54172.85</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP|SS-02-B0DNJP9T35| Auto</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2013.19</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>8239</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>11861.86</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_Auto_CAP-05_B0GN86G345</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>5684.54</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>7779</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>25671.16</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_KT - MC-01</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>3605.5</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>10251</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_KT_ST-02_B0GN94YDY2_CG_MV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0CYSLCRQS - Sofa &amp; Carpet Vacuum Cleaner - KT - Exact11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1820,12 +1808,12 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT - MC-01</t>
+          <t>Nexlev - B0D383WQPB -  Foldable Garment Steamer 0 - SP - PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1848,22 +1836,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>221.76</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>17379</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1876,53 +1864,53 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-03_B0GN8WW6BC</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>938.5600000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>6884</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>4806.780000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
+          <t>Nexlev - B0D63FKYZ5 - Scalp Massager - Broad</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>624.75</v>
+        <v>348.19</v>
       </c>
       <c r="E53" t="n">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="F53" t="n">
-        <v>23360</v>
+        <v>7655</v>
       </c>
       <c r="G53" t="n">
-        <v>668.64</v>
+        <v>951.4299999999999</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -1932,12 +1920,12 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPMX152 - Handheld Garment Steamer - KT - Comp - Multi Ad Group 07</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1960,134 +1948,134 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>8823.559999999999</v>
+        <v>456.61</v>
       </c>
       <c r="E55" t="n">
-        <v>594</v>
+        <v>33</v>
       </c>
       <c r="F55" t="n">
-        <v>66936</v>
+        <v>13088</v>
       </c>
       <c r="G55" t="n">
-        <v>59001.66</v>
+        <v>3542.35</v>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2340.72</v>
+        <v>730.4400000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
-        <v>10268</v>
+        <v>14542</v>
       </c>
       <c r="G56" t="n">
-        <v>11861.86</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
+          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6798.27</v>
+        <v>548.5599999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>542</v>
+        <v>48</v>
       </c>
       <c r="F57" t="n">
-        <v>8925</v>
+        <v>9127</v>
       </c>
       <c r="G57" t="n">
-        <v>41895.72</v>
+        <v>2116.94</v>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3967.4</v>
+        <v>68.16</v>
       </c>
       <c r="E58" t="n">
-        <v>259</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>11214</v>
+        <v>6864</v>
       </c>
       <c r="G58" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev - B0CYSLCRQS - Sofa &amp; Carpet Vacuum Cleaner - KT - Exact11</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>228.14</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2100,50 +2088,50 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev - B0D25LNDSY - Rechargeable Electric Toothbrush 0 - SP - CT</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1279.7</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>32320</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>4517.8</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB -  Foldable Garment Steamer - KT - Exact 07</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>396.76</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2509</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2156,12 +2144,12 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB -  Foldable Garment Steamer 0 - SP - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2184,134 +2172,134 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Foldable Garment Steamer - SP - KT 1</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>3071.23</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>75110</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>421.85</v>
+        <v>1581.34</v>
       </c>
       <c r="E64" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="F64" t="n">
-        <v>23368</v>
+        <v>7487</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2826.27</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1195.74</v>
+        <v>1811.91</v>
       </c>
       <c r="E65" t="n">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="F65" t="n">
-        <v>8658</v>
+        <v>7773</v>
       </c>
       <c r="G65" t="n">
-        <v>4806.780000000001</v>
+        <v>2826.27</v>
       </c>
       <c r="H65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev - B0D63FKYZ5 - Scalp Massager - Broad</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>412.45</v>
+        <v>1602.07</v>
       </c>
       <c r="E66" t="n">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="F66" t="n">
-        <v>13128</v>
+        <v>26862</v>
       </c>
       <c r="G66" t="n">
-        <v>951.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>269.76</v>
+        <v>2025.73</v>
       </c>
       <c r="E67" t="n">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="F67" t="n">
-        <v>4842</v>
+        <v>9500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2324,50 +2312,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>766.3199999999999</v>
+        <v>254.56</v>
       </c>
       <c r="E68" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>30535</v>
+        <v>7193</v>
       </c>
       <c r="G68" t="n">
-        <v>3542.35</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Exact</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>742.64</v>
+        <v>135.56</v>
       </c>
       <c r="E69" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F69" t="n">
-        <v>15102</v>
+        <v>3316</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2380,50 +2368,50 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>732.16</v>
+        <v>244.83</v>
       </c>
       <c r="E70" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F70" t="n">
-        <v>13186</v>
+        <v>10009</v>
       </c>
       <c r="G70" t="n">
-        <v>3120.33</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - BM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>68.16</v>
+        <v>178.44</v>
       </c>
       <c r="E71" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F71" t="n">
-        <v>6864</v>
+        <v>5619</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2436,22 +2424,22 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - Exact</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>228.14</v>
+        <v>46.05</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>374</v>
+        <v>672</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2464,50 +2452,50 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1369.94</v>
+        <v>1142.09</v>
       </c>
       <c r="E73" t="n">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="F73" t="n">
-        <v>34143</v>
+        <v>3474</v>
       </c>
       <c r="G73" t="n">
-        <v>4517.8</v>
+        <v>1719.5</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>396.76</v>
+        <v>2260.02</v>
       </c>
       <c r="E74" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="F74" t="n">
-        <v>2509</v>
+        <v>8060</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2520,134 +2508,134 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
+          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>4426.690000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>14326</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>24997.14</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3295.94</v>
+        <v>158.16</v>
       </c>
       <c r="E76" t="n">
-        <v>447</v>
+        <v>14</v>
       </c>
       <c r="F76" t="n">
-        <v>78254</v>
+        <v>6823</v>
       </c>
       <c r="G76" t="n">
-        <v>10680.51</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1666.15</v>
+        <v>2830.91</v>
       </c>
       <c r="E77" t="n">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="F77" t="n">
-        <v>8375</v>
+        <v>24021</v>
       </c>
       <c r="G77" t="n">
-        <v>2826.27</v>
+        <v>10167.8</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1811.91</v>
+        <v>1924.39</v>
       </c>
       <c r="E78" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F78" t="n">
-        <v>7856</v>
+        <v>14663</v>
       </c>
       <c r="G78" t="n">
-        <v>2826.27</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1789.41</v>
+        <v>1659.48</v>
       </c>
       <c r="E79" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>27593</v>
+        <v>7221</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2660,22 +2648,22 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2042.25</v>
+        <v>1980.39</v>
       </c>
       <c r="E80" t="n">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>9655</v>
+        <v>1344</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2688,22 +2676,22 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>415.13</v>
+        <v>1522.36</v>
       </c>
       <c r="E81" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="F81" t="n">
-        <v>14087</v>
+        <v>36461</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2716,22 +2704,22 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Exact</t>
+          <t>Nexlev - B0DQCWRG3H - Ionic 3 in 1 Hot Air Brush - Broad1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>217.96</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>6026</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2744,22 +2732,22 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>282.09</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="E83" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>11129</v>
+        <v>7783</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2772,106 +2760,106 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - BM</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - BM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>337.19</v>
+        <v>83.09</v>
       </c>
       <c r="E84" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F84" t="n">
-        <v>9988</v>
+        <v>599</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>856.1900000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>52.68</v>
+        <v>1663.11</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F85" t="n">
-        <v>1079</v>
+        <v>27278</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>30333.9</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - PT</t>
+          <t>Nexlev - B0DVC8NYY2 -  Ultrasonic Cool Mist Humidifier - KT - Excat 00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1530.9</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>4403</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1719.5</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
+          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2715.39</v>
+        <v>664.73</v>
       </c>
       <c r="E87" t="n">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="F87" t="n">
-        <v>10496</v>
+        <v>2827</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2884,106 +2872,106 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4868.559999999999</v>
+        <v>1966.49</v>
       </c>
       <c r="E88" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="F88" t="n">
-        <v>15459</v>
+        <v>38055</v>
       </c>
       <c r="G88" t="n">
-        <v>24997.14</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>231.41</v>
+        <v>2925.08</v>
       </c>
       <c r="E89" t="n">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="F89" t="n">
-        <v>12895</v>
+        <v>13254</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>10462.7</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - KT - Comp - Multi Ad Group - 01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3184.51</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>26860</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>10167.8</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2252.31</v>
+        <v>1077.96</v>
       </c>
       <c r="E91" t="n">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="F91" t="n">
-        <v>16307</v>
+        <v>4002</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2996,22 +2984,22 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1909.24</v>
+        <v>1573.99</v>
       </c>
       <c r="E92" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F92" t="n">
-        <v>8590</v>
+        <v>41752</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3024,50 +3012,50 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2355.4</v>
+        <v>9109.17</v>
       </c>
       <c r="E93" t="n">
-        <v>65</v>
+        <v>447</v>
       </c>
       <c r="F93" t="n">
-        <v>1690</v>
+        <v>45542</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>32490.64</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner 01 - KT - Branded - Phrase - Exact</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1889.78</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>46990</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3080,124 +3068,124 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev - B0DQCWRG3H - Ionic 3 in 1 Hot Air Brush - Broad1</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>3913.74</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>111755</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>6099.16</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>113.87</v>
+        <v>2300.22</v>
       </c>
       <c r="E96" t="n">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="F96" t="n">
-        <v>15369</v>
+        <v>33784</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>8132.21</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - BM</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>178.43</v>
+        <v>990.8200000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="F97" t="n">
-        <v>2482</v>
+        <v>31960</v>
       </c>
       <c r="G97" t="n">
-        <v>1664.76</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0GN86G345 -  Car Air Purifier - KT - Multi Ad Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1886.07</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>31126</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>30333.9</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC8NYY2 -  Ultrasonic Cool Mist Humidifier - KT - Excat 00</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3207,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3220,22 +3208,22 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>858.0600000000001</v>
+        <v>7.3</v>
       </c>
       <c r="E100" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>3362</v>
+        <v>29</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3248,22 +3236,22 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
+          <t>Nexlev - Stand Mixer - SP - CT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2404.45</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>46364</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3276,78 +3264,78 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev -B0CDPMX152- Garment Steamer -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3434.88</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>16638</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>13131.34</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - KT - Comp - Multi Ad Group - 01</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>6775.78</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>18152</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>12835.58</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1344.91</v>
+        <v>1318.11</v>
       </c>
       <c r="E104" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F104" t="n">
-        <v>4667</v>
+        <v>2999</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3360,302 +3348,302 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1948.47</v>
+        <v>1315.53</v>
       </c>
       <c r="E105" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>50589</v>
+        <v>6697</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10020.26</v>
+        <v>1188.01</v>
       </c>
       <c r="E106" t="n">
-        <v>489</v>
+        <v>108</v>
       </c>
       <c r="F106" t="n">
-        <v>51390</v>
+        <v>2335</v>
       </c>
       <c r="G106" t="n">
-        <v>35032.17</v>
+        <v>2541.53</v>
       </c>
       <c r="H106" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner 01 - KT - Branded - Phrase - Exact</t>
+          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>528.23</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>2432</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>619.49</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4419.89</v>
+        <v>936.26</v>
       </c>
       <c r="E108" t="n">
-        <v>327</v>
+        <v>25</v>
       </c>
       <c r="F108" t="n">
-        <v>124692</v>
+        <v>2302</v>
       </c>
       <c r="G108" t="n">
-        <v>10040.68</v>
+        <v>1439.83</v>
       </c>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2508.02</v>
+        <v>1446.1</v>
       </c>
       <c r="E109" t="n">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="F109" t="n">
-        <v>37588</v>
+        <v>2566</v>
       </c>
       <c r="G109" t="n">
-        <v>8132.21</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1390.99</v>
+        <v>1208</v>
       </c>
       <c r="E110" t="n">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="F110" t="n">
-        <v>40636</v>
+        <v>1550</v>
       </c>
       <c r="G110" t="n">
-        <v>1930.51</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN86G345 -  Car Air Purifier - KT - Multi Ad Group</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>8444.370000000001</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>45089</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>45095.72</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>3209.32</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="F112" t="n">
-        <v>174</v>
+        <v>3076</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>8048.299999999999</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7.3</v>
+        <v>161.27</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>29</v>
+        <v>1387</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>6902.15</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nexlev - Stand Mixer - SP - CT</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>199.01</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>2864</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>6608.48</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPMX152- Garment Steamer -SP-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>149.75</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1212</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3668,81 +3656,81 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7429.84</v>
+        <v>286.08</v>
       </c>
       <c r="E116" t="n">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="F116" t="n">
-        <v>18605</v>
+        <v>4948</v>
       </c>
       <c r="G116" t="n">
-        <v>12835.58</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1492.55</v>
+        <v>1083.94</v>
       </c>
       <c r="E117" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F117" t="n">
-        <v>6924</v>
+        <v>32188</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2879.66</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1605.63</v>
+        <v>365.92</v>
       </c>
       <c r="E118" t="n">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F118" t="n">
-        <v>8835</v>
+        <v>994</v>
       </c>
       <c r="G118" t="n">
-        <v>338.14</v>
+        <v>1270.34</v>
       </c>
       <c r="H118" t="n">
         <v>1</v>
@@ -3752,134 +3740,134 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1337.25</v>
+        <v>225.07</v>
       </c>
       <c r="E119" t="n">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F119" t="n">
-        <v>2726</v>
+        <v>2322</v>
       </c>
       <c r="G119" t="n">
-        <v>2541.53</v>
+        <v>4062.72</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>627.4300000000001</v>
+        <v>5.86</v>
       </c>
       <c r="E120" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>3128</v>
+        <v>62</v>
       </c>
       <c r="G120" t="n">
-        <v>1198.3</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
+          <t>Nexlev-B0CDPMX152-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1211.04</v>
+        <v>70.78</v>
       </c>
       <c r="E121" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F121" t="n">
-        <v>3502</v>
+        <v>1103</v>
       </c>
       <c r="G121" t="n">
-        <v>2844.07</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1757.1</v>
+        <v>2892.06</v>
       </c>
       <c r="E122" t="n">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="F122" t="n">
-        <v>2791</v>
+        <v>10314</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1529.19</v>
+        <v>2392.24</v>
       </c>
       <c r="E123" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F123" t="n">
-        <v>1985</v>
+        <v>14138</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3892,78 +3880,78 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>9810.969999999999</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>54038</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>52720.28</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3718.11</v>
+        <v>1268.02</v>
       </c>
       <c r="E125" t="n">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="F125" t="n">
-        <v>3564</v>
+        <v>5676</v>
       </c>
       <c r="G125" t="n">
-        <v>13258.47</v>
+        <v>2456.78</v>
       </c>
       <c r="H125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1427.93</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>10126</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3976,218 +3964,218 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>200.59</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>6902.15</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>225.91</v>
+        <v>1271.1</v>
       </c>
       <c r="E128" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F128" t="n">
-        <v>3246</v>
+        <v>5548</v>
       </c>
       <c r="G128" t="n">
-        <v>6608.48</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>179.2</v>
+        <v>464.74</v>
       </c>
       <c r="E129" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F129" t="n">
-        <v>1461</v>
+        <v>7315</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1238.98</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>340.14</v>
+        <v>556.7</v>
       </c>
       <c r="E130" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="F130" t="n">
-        <v>5966</v>
+        <v>11426</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3551.7</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1459.35</v>
+        <v>160.44</v>
       </c>
       <c r="E131" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="F131" t="n">
-        <v>41248</v>
+        <v>3650</v>
       </c>
       <c r="G131" t="n">
-        <v>5557.62</v>
+        <v>3197.46</v>
       </c>
       <c r="H131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>398.55</v>
+        <v>13.39</v>
       </c>
       <c r="E132" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>1256</v>
+        <v>517</v>
       </c>
       <c r="G132" t="n">
-        <v>1270.34</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>293.15</v>
+        <v>1956.25</v>
       </c>
       <c r="E133" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F133" t="n">
-        <v>3121</v>
+        <v>5761</v>
       </c>
       <c r="G133" t="n">
-        <v>5289.84</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5.86</v>
+        <v>266.56</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F134" t="n">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4200,106 +4188,106 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>81.67999999999999</v>
+        <v>464.45</v>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="F135" t="n">
-        <v>1163</v>
+        <v>5463</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>2093.34</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3530.36</v>
+        <v>57.27</v>
       </c>
       <c r="E136" t="n">
-        <v>284</v>
+        <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>12324</v>
+        <v>190</v>
       </c>
       <c r="G136" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-Auto</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2893.86</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>18457</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>23.35</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4312,50 +4300,50 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1459.46</v>
+        <v>1994.63</v>
       </c>
       <c r="E139" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F139" t="n">
-        <v>6979</v>
+        <v>32781</v>
       </c>
       <c r="G139" t="n">
-        <v>2456.78</v>
+        <v>4312.71</v>
       </c>
       <c r="H139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1676.43</v>
+        <v>726.0599999999999</v>
       </c>
       <c r="E140" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F140" t="n">
-        <v>11610</v>
+        <v>11808</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4368,22 +4356,22 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>569.5700000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>3605</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4396,162 +4384,162 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1752.66</v>
+        <v>149.8</v>
       </c>
       <c r="E142" t="n">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="F142" t="n">
-        <v>8554</v>
+        <v>913</v>
       </c>
       <c r="G142" t="n">
-        <v>2367.8</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>593.05</v>
+        <v>1874.23</v>
       </c>
       <c r="E143" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F143" t="n">
-        <v>8346</v>
+        <v>12555</v>
       </c>
       <c r="G143" t="n">
-        <v>1238.98</v>
+        <v>2541.53</v>
       </c>
       <c r="H143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>697.46</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>13360</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>3551.7</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>263.23</v>
+        <v>1121.73</v>
       </c>
       <c r="E145" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F145" t="n">
-        <v>5916</v>
+        <v>1437</v>
       </c>
       <c r="G145" t="n">
-        <v>3197.46</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>13.39</v>
+        <v>851.7</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="F146" t="n">
-        <v>607</v>
+        <v>7724</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>7236.2</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2736.15</v>
+        <v>1077.5</v>
       </c>
       <c r="E147" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="F147" t="n">
-        <v>8612</v>
+        <v>2660</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4564,22 +4552,22 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0DNJP9T35-Spin Scrubber- SP -KT-Phrase</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>324.43</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4592,78 +4580,78 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>563.36</v>
+        <v>3154.81</v>
       </c>
       <c r="E149" t="n">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="F149" t="n">
-        <v>5985</v>
+        <v>28854</v>
       </c>
       <c r="G149" t="n">
-        <v>2093.34</v>
+        <v>17200</v>
       </c>
       <c r="H149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>57.27</v>
+        <v>1259.88</v>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="F150" t="n">
-        <v>229</v>
+        <v>3001</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nexlev-B0D845B2DG-Lint Remover-SP-Auto</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>697.29</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1759</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4676,22 +4664,22 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>43.25</v>
+        <v>2720.39</v>
       </c>
       <c r="E152" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="F152" t="n">
-        <v>300</v>
+        <v>8554</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4704,134 +4692,134 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2284.46</v>
+        <v>1302.64</v>
       </c>
       <c r="E153" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="F153" t="n">
-        <v>37700</v>
+        <v>19947</v>
       </c>
       <c r="G153" t="n">
-        <v>4312.71</v>
+        <v>5209.32</v>
       </c>
       <c r="H153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>882.48</v>
+        <v>2135.97</v>
       </c>
       <c r="E154" t="n">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="F154" t="n">
-        <v>13208</v>
+        <v>39114</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>6920.34</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>797.0700000000001</v>
+        <v>306.73</v>
       </c>
       <c r="E155" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F155" t="n">
-        <v>5318</v>
+        <v>16152</v>
       </c>
       <c r="G155" t="n">
-        <v>2152.54</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>219.1</v>
+        <v>1488.64</v>
       </c>
       <c r="E156" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F156" t="n">
-        <v>997</v>
+        <v>17068</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>5099.15</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1994.26</v>
+        <v>513.51</v>
       </c>
       <c r="E157" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="F157" t="n">
-        <v>12943</v>
+        <v>3139</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4844,50 +4832,50 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>4065.9</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>9739</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>12538.13</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1378.36</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>1558</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4900,162 +4888,162 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1039.08</v>
+        <v>222</v>
       </c>
       <c r="E160" t="n">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="F160" t="n">
-        <v>9253</v>
+        <v>1479</v>
       </c>
       <c r="G160" t="n">
-        <v>11320</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1805.51</v>
+        <v>5026.36</v>
       </c>
       <c r="E161" t="n">
-        <v>63</v>
+        <v>296</v>
       </c>
       <c r="F161" t="n">
-        <v>3894</v>
+        <v>14305</v>
       </c>
       <c r="G161" t="n">
-        <v>2665.71</v>
+        <v>16775.41</v>
       </c>
       <c r="H161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJP9T35-Spin Scrubber- SP -KT-Phrase</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>4213.450000000001</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>157697</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>14209.32</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4005.18</v>
+        <v>245.7</v>
       </c>
       <c r="E163" t="n">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="F163" t="n">
-        <v>36978</v>
+        <v>15173</v>
       </c>
       <c r="G163" t="n">
-        <v>22028.81</v>
+        <v>6099.15</v>
       </c>
       <c r="H163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1384.58</v>
+        <v>408.59</v>
       </c>
       <c r="E164" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="F164" t="n">
-        <v>3538</v>
+        <v>3468</v>
       </c>
       <c r="G164" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>850.4</v>
+        <v>372.84</v>
       </c>
       <c r="E165" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F165" t="n">
-        <v>2244</v>
+        <v>5675</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5068,218 +5056,218 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3397.64</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>10649</v>
+        <v>7</v>
       </c>
       <c r="G166" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1605.81</v>
+        <v>40.87</v>
       </c>
       <c r="E167" t="n">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="F167" t="n">
-        <v>23362</v>
+        <v>3311</v>
       </c>
       <c r="G167" t="n">
-        <v>5209.32</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2434.87</v>
+        <v>19.31</v>
       </c>
       <c r="E168" t="n">
-        <v>235</v>
+        <v>3</v>
       </c>
       <c r="F168" t="n">
-        <v>47320</v>
+        <v>2343</v>
       </c>
       <c r="G168" t="n">
-        <v>8044.07</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>338.94</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>17514</v>
+        <v>55</v>
       </c>
       <c r="G169" t="n">
-        <v>4914.4</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2047.91</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>28906</v>
+        <v>23</v>
       </c>
       <c r="G170" t="n">
-        <v>10013.56</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>532.4</v>
+        <v>13.2</v>
       </c>
       <c r="E171" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>3634</v>
+        <v>1144</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4598.99</v>
+        <v>6.69</v>
       </c>
       <c r="E172" t="n">
-        <v>221</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>11679</v>
+        <v>42</v>
       </c>
       <c r="G172" t="n">
-        <v>9657.620000000001</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5292,22 +5280,22 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>414.03</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>1751</v>
+        <v>18</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -5320,106 +5308,106 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>7188.77</v>
+        <v>14.9</v>
       </c>
       <c r="E175" t="n">
-        <v>429</v>
+        <v>3</v>
       </c>
       <c r="F175" t="n">
-        <v>21714</v>
+        <v>86</v>
       </c>
       <c r="G175" t="n">
-        <v>32872.04</v>
+        <v>1295.76</v>
       </c>
       <c r="H175" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4832.73</v>
+        <v>21.14</v>
       </c>
       <c r="E176" t="n">
-        <v>368</v>
+        <v>4</v>
       </c>
       <c r="F176" t="n">
-        <v>183566</v>
+        <v>1159</v>
       </c>
       <c r="G176" t="n">
-        <v>16139.83</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>302.16</v>
+        <v>13.33</v>
       </c>
       <c r="E177" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>19040</v>
+        <v>51</v>
       </c>
       <c r="G177" t="n">
-        <v>6099.15</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>592.27</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>5436</v>
+        <v>61</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5432,22 +5420,22 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>506.68</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>6898</v>
+        <v>59</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5465,17 +5453,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F180" t="n">
-        <v>7</v>
+        <v>479</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5493,17 +5481,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>40.87</v>
+        <v>6.8</v>
       </c>
       <c r="E181" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>3311</v>
+        <v>366</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5521,17 +5509,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>19.31</v>
+        <v>30.89</v>
       </c>
       <c r="E182" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>2343</v>
+        <v>496</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5549,17 +5537,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
+        <v>58.25</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F183" t="n">
-        <v>55</v>
+        <v>354</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5577,17 +5565,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>23</v>
+        <v>243</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5605,20 +5593,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>13.2</v>
+        <v>31.38</v>
       </c>
       <c r="E185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F185" t="n">
-        <v>1144</v>
+        <v>805</v>
       </c>
       <c r="G185" t="n">
-        <v>677.12</v>
+        <v>1778.81</v>
       </c>
       <c r="H185" t="n">
         <v>1</v>
@@ -5633,17 +5621,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>6.69</v>
+        <v>40.5</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>42</v>
+        <v>444</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5661,17 +5649,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5689,17 +5677,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5717,23 +5705,23 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="G189" t="n">
-        <v>1295.76</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -5745,17 +5733,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>21.14</v>
+        <v>21.89</v>
       </c>
       <c r="E190" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F190" t="n">
-        <v>1159</v>
+        <v>48</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5773,17 +5761,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>13.33</v>
+        <v>107.07</v>
       </c>
       <c r="E191" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F191" t="n">
-        <v>51</v>
+        <v>2509</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5801,17 +5789,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>9.33</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F192" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5829,7 +5817,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -5839,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5857,17 +5845,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>479</v>
+        <v>5</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5885,17 +5873,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>6.8</v>
+        <v>13.6</v>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" t="n">
-        <v>366</v>
+        <v>59</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5913,17 +5901,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>30.89</v>
+        <v>6.19</v>
       </c>
       <c r="E196" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>496</v>
+        <v>45</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5941,17 +5929,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>58.25</v>
+        <v>17.74</v>
       </c>
       <c r="E197" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F197" t="n">
-        <v>354</v>
+        <v>770</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5969,17 +5957,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>243</v>
+        <v>4</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5997,23 +5985,23 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>31.38</v>
+        <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G199" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -6025,17 +6013,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -6053,17 +6041,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F201" t="n">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6081,23 +6069,23 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6.8</v>
+        <v>6.78</v>
       </c>
       <c r="E202" t="n">
         <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>6</v>
+        <v>3494</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>2668.64</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -6109,17 +6097,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>5</v>
+        <v>512</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6137,17 +6125,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>21.89</v>
+        <v>14.49</v>
       </c>
       <c r="E204" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F204" t="n">
-        <v>48</v>
+        <v>296</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6165,17 +6153,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>107.07</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>2509</v>
+        <v>65</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6193,17 +6181,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6221,17 +6209,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6249,17 +6237,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F208" t="n">
-        <v>5</v>
+        <v>565</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6277,17 +6265,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6305,17 +6293,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>6.19</v>
+        <v>14.93</v>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F210" t="n">
-        <v>45</v>
+        <v>2303</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6333,17 +6321,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>17.74</v>
+        <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>770</v>
+        <v>52</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6361,7 +6349,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -6371,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6389,17 +6377,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>31</v>
+        <v>282</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6417,17 +6405,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="E214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F214" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6445,17 +6433,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>25.45</v>
+        <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6473,23 +6461,23 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>6.78</v>
+        <v>13.47</v>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F216" t="n">
-        <v>3494</v>
+        <v>1509</v>
       </c>
       <c r="G216" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -6501,17 +6489,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>4.79</v>
+        <v>75.95</v>
       </c>
       <c r="E217" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F217" t="n">
-        <v>512</v>
+        <v>791</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6524,22 +6512,22 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>14.49</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6552,12 +6540,12 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -6567,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>65</v>
+        <v>551</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6580,22 +6568,22 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
-        <v>94</v>
+        <v>973</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6608,22 +6596,22 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6636,22 +6624,22 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>13.1</v>
+        <v>3</v>
       </c>
       <c r="E222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>565</v>
+        <v>3005</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6664,22 +6652,22 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="E223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F223" t="n">
-        <v>200</v>
+        <v>884</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6692,22 +6680,22 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>14.93</v>
+        <v>1.57</v>
       </c>
       <c r="E224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>2303</v>
+        <v>314</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6720,12 +6708,12 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -6735,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6748,22 +6736,22 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F226" t="n">
-        <v>129</v>
+        <v>410</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6776,22 +6764,22 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="E227" t="n">
         <v>1</v>
       </c>
       <c r="F227" t="n">
-        <v>282</v>
+        <v>673</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6804,22 +6792,22 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="E228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F228" t="n">
-        <v>115</v>
+        <v>578</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6832,12 +6820,12 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -6847,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>54</v>
+        <v>4764</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6860,22 +6848,22 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>13.47</v>
+        <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>1509</v>
+        <v>307</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6888,22 +6876,22 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>75.95</v>
+        <v>4.23</v>
       </c>
       <c r="E231" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F231" t="n">
-        <v>791</v>
+        <v>392</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6921,17 +6909,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F232" t="n">
-        <v>19</v>
+        <v>621</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6949,17 +6937,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>7.69</v>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F233" t="n">
-        <v>552</v>
+        <v>143</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6977,17 +6965,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>973</v>
+        <v>163</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -7005,17 +6993,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7033,17 +7021,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>3005</v>
+        <v>74</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7061,17 +7049,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>6.68</v>
+        <v>347.92</v>
       </c>
       <c r="E237" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="F237" t="n">
-        <v>884</v>
+        <v>12554</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7089,23 +7077,23 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1.57</v>
+        <v>465.05</v>
       </c>
       <c r="E238" t="n">
+        <v>173</v>
+      </c>
+      <c r="F238" t="n">
+        <v>18401</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1944.07</v>
+      </c>
+      <c r="H238" t="n">
         <v>1</v>
-      </c>
-      <c r="F238" t="n">
-        <v>314</v>
-      </c>
-      <c r="G238" t="n">
-        <v>0</v>
-      </c>
-      <c r="H238" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -7117,17 +7105,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7145,17 +7133,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>8.92</v>
+        <v>14.85</v>
       </c>
       <c r="E240" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F240" t="n">
-        <v>410</v>
+        <v>1843</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7173,17 +7161,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>673</v>
+        <v>284</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7201,17 +7189,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>8.6</v>
+        <v>50.64</v>
       </c>
       <c r="E242" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F242" t="n">
-        <v>578</v>
+        <v>2487</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -7229,17 +7217,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F243" t="n">
-        <v>4764</v>
+        <v>601</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7257,17 +7245,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F244" t="n">
-        <v>307</v>
+        <v>431</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7285,17 +7273,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>392</v>
+        <v>47</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7313,17 +7301,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>622</v>
+        <v>3</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -7341,17 +7329,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>7.69</v>
+        <v>3</v>
       </c>
       <c r="E247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>143</v>
+        <v>496</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7369,7 +7357,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -7379,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>163</v>
+        <v>530</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -7397,17 +7385,17 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F249" t="n">
-        <v>69</v>
+        <v>1481</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -7425,7 +7413,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -7435,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -7453,17 +7441,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>348.92</v>
+        <v>2.6</v>
       </c>
       <c r="E251" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="F251" t="n">
-        <v>12556</v>
+        <v>2938</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7481,23 +7469,23 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>465.05</v>
+        <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>18404</v>
+        <v>10</v>
       </c>
       <c r="G252" t="n">
-        <v>1944.07</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -7509,17 +7497,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="E253" t="n">
         <v>1</v>
       </c>
       <c r="F253" t="n">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7537,17 +7525,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>14.85</v>
+        <v>5.08</v>
       </c>
       <c r="E254" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F254" t="n">
-        <v>1843</v>
+        <v>975</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7565,17 +7553,17 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7593,17 +7581,17 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>50.64</v>
+        <v>1.29</v>
       </c>
       <c r="E256" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>2487</v>
+        <v>375</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7621,17 +7609,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E257" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>601</v>
+        <v>83</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -7649,23 +7637,23 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>11.3</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="E258" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F258" t="n">
-        <v>432</v>
+        <v>43</v>
       </c>
       <c r="G258" t="n">
-        <v>0</v>
+        <v>211.02</v>
       </c>
       <c r="H258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -7677,17 +7665,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F259" t="n">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -7705,23 +7693,23 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>49.46</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F260" t="n">
-        <v>3</v>
+        <v>592</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>211.02</v>
       </c>
       <c r="H260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -7733,17 +7721,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E261" t="n">
         <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>496</v>
+        <v>31</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -7761,17 +7749,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>24.87</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F262" t="n">
-        <v>530</v>
+        <v>3218</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7789,17 +7777,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F263" t="n">
-        <v>1481</v>
+        <v>367</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -7817,17 +7805,17 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F264" t="n">
-        <v>2</v>
+        <v>403</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -7845,17 +7833,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2.6</v>
+        <v>11.79</v>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F265" t="n">
-        <v>2938</v>
+        <v>1134</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -7873,17 +7861,17 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F266" t="n">
-        <v>10</v>
+        <v>363</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -7901,17 +7889,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1.33</v>
+        <v>8.07</v>
       </c>
       <c r="E267" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F267" t="n">
-        <v>28</v>
+        <v>537</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -7929,17 +7917,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>5.08</v>
+        <v>4.3</v>
       </c>
       <c r="E268" t="n">
         <v>2</v>
       </c>
       <c r="F268" t="n">
-        <v>975</v>
+        <v>1271</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -7957,17 +7945,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1.63</v>
+        <v>18.88</v>
       </c>
       <c r="E269" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F269" t="n">
-        <v>151</v>
+        <v>383</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -7980,22 +7968,22 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -8008,12 +7996,12 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -8023,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -8036,50 +8024,50 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>5.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="E272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F272" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G272" t="n">
-        <v>211.02</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="E273" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>184</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -8092,50 +8080,50 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>49.46</v>
+        <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>592</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>211.02</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
         <v>1</v>
-      </c>
-      <c r="F275" t="n">
-        <v>31</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -8148,22 +8136,22 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>24.87</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>3218</v>
+        <v>6</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -8176,12 +8164,12 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -8191,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -8204,22 +8192,22 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>403</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -8232,22 +8220,22 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>11.79</v>
+        <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>1134</v>
+        <v>1</v>
       </c>
       <c r="G279" t="n">
         <v>0</v>
@@ -8260,22 +8248,22 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>363</v>
+        <v>4</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8288,22 +8276,22 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>8.07</v>
+        <v>0</v>
       </c>
       <c r="E281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>537</v>
+        <v>1</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -8316,22 +8304,22 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="E282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F282" t="n">
-        <v>1271</v>
+        <v>0</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -8344,22 +8332,22 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>18.88</v>
+        <v>0</v>
       </c>
       <c r="E283" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F283" t="n">
-        <v>383</v>
+        <v>1</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -8377,7 +8365,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -8387,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -8405,7 +8393,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -8415,7 +8403,7 @@
         <v>0</v>
       </c>
       <c r="F285" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
@@ -8433,17 +8421,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" t="n">
         <v>1</v>
-      </c>
-      <c r="F286" t="n">
-        <v>5</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -8461,7 +8449,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -8471,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -8484,40 +8472,40 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>6282.780000000001</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="F288" t="n">
-        <v>1</v>
+        <v>27576</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>42459.29</v>
       </c>
       <c r="H288" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -8527,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -8540,12 +8528,12 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Steam Cleaner-B0F43P6D23-KW(3)-SP-Exact</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -8555,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="F290" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G290" t="n">
         <v>0</v>
@@ -8568,22 +8556,22 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
+        <v>16.74</v>
       </c>
       <c r="E291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G291" t="n">
         <v>0</v>
@@ -8596,22 +8584,22 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
+        <v>154.83</v>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F292" t="n">
-        <v>1</v>
+        <v>2636</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -8624,22 +8612,22 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>1045</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -8652,50 +8640,50 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>101.34</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F294" t="n">
-        <v>4</v>
+        <v>729</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>2668.64</v>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>657.84</v>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F295" t="n">
-        <v>1</v>
+        <v>3933</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -8708,22 +8696,22 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
+        <v>428.05</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -8736,22 +8724,22 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0</v>
+        <v>253.33</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F297" t="n">
-        <v>1</v>
+        <v>1437</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -8764,22 +8752,22 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>652.8</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F298" t="n">
-        <v>1</v>
+        <v>13718</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -8792,12 +8780,12 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -8807,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -8820,22 +8808,22 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0</v>
+        <v>58.79</v>
       </c>
       <c r="E300" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
@@ -8848,68 +8836,68 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>1270.06</v>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>33916</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>5166.959999999999</v>
       </c>
       <c r="H301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>6883.79</v>
+        <v>0</v>
       </c>
       <c r="E302" t="n">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="F302" t="n">
-        <v>30755</v>
+        <v>3</v>
       </c>
       <c r="G302" t="n">
-        <v>42459.29</v>
+        <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -8919,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -8932,22 +8920,22 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Nexlev-Steam Cleaner-B0F43P6D23-KW(3)-SP-Exact</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0</v>
+        <v>30.68</v>
       </c>
       <c r="E304" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F304" t="n">
-        <v>4</v>
+        <v>494</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -8960,22 +8948,22 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>16.74</v>
+        <v>62.87</v>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F305" t="n">
-        <v>18</v>
+        <v>435</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
@@ -8988,22 +8976,22 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>154.83</v>
+        <v>21.4</v>
       </c>
       <c r="E306" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>2636</v>
+        <v>13</v>
       </c>
       <c r="G306" t="n">
         <v>0</v>
@@ -9016,35 +9004,35 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>23</v>
+        <v>350.15</v>
       </c>
       <c r="E307" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F307" t="n">
-        <v>1045</v>
+        <v>290</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>2668.64</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9053,41 +9041,41 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>101.34</v>
+        <v>262</v>
       </c>
       <c r="E308" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F308" t="n">
-        <v>729</v>
+        <v>178</v>
       </c>
       <c r="G308" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(1)-Exact-SP</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>657.84</v>
+        <v>0</v>
       </c>
       <c r="E309" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F309" t="n">
-        <v>3933</v>
+        <v>5</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
@@ -9100,22 +9088,22 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(11)-SP-Exact</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>428.05</v>
+        <v>0</v>
       </c>
       <c r="E310" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F310" t="n">
-        <v>1464</v>
+        <v>53</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -9128,22 +9116,22 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>253.33</v>
+        <v>338.2</v>
       </c>
       <c r="E311" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F311" t="n">
-        <v>1437</v>
+        <v>143</v>
       </c>
       <c r="G311" t="n">
         <v>0</v>
@@ -9156,22 +9144,22 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-SP-Exact</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>652.8</v>
+        <v>0</v>
       </c>
       <c r="E312" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F312" t="n">
-        <v>13719</v>
+        <v>2</v>
       </c>
       <c r="G312" t="n">
         <v>0</v>
@@ -9184,22 +9172,22 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW-Phrase-SP</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>40.45</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F313" t="n">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="G313" t="n">
         <v>0</v>
@@ -9212,7 +9200,7 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
+          <t>Nexliv-Steam Cleaner/-B0F43P6D23-HG Exact(1)-SP</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9221,13 +9209,13 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>58.79</v>
+        <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
@@ -9240,40 +9228,40 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1270.06</v>
+        <v>0</v>
       </c>
       <c r="E315" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F315" t="n">
-        <v>33917</v>
+        <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>5166.959999999999</v>
+        <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -9283,7 +9271,7 @@
         <v>0</v>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
@@ -9296,12 +9284,12 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexliv-Steam Mop Floor-B0DNJS23HS-BM-KW(1)-SP</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -9311,7 +9299,7 @@
         <v>0</v>
       </c>
       <c r="F317" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="G317" t="n">
         <v>0</v>
@@ -9324,22 +9312,22 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexliv-steam cleaner for kitchen -KW(3)-BM-SP</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>30.68</v>
+        <v>104.33</v>
       </c>
       <c r="E318" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F318" t="n">
-        <v>494</v>
+        <v>23</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
@@ -9352,22 +9340,22 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexlive Steam Cleaner-B0F43P6D23-KW(1)BM-SP</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>62.87</v>
+        <v>18.77</v>
       </c>
       <c r="E319" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F319" t="n">
-        <v>435</v>
+        <v>7</v>
       </c>
       <c r="G319" t="n">
         <v>0</v>
@@ -9380,22 +9368,22 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-BM-SP</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>21.4</v>
+        <v>911.54</v>
       </c>
       <c r="E320" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="F320" t="n">
-        <v>13</v>
+        <v>10457</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
@@ -9408,50 +9396,50 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>350.15</v>
+        <v>457.8</v>
       </c>
       <c r="E321" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F321" t="n">
-        <v>290</v>
+        <v>9060</v>
       </c>
       <c r="G321" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexlive-Portable Cordless Lint Remover-B0FT8R24QM-Phrase-SP</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>262</v>
+        <v>21.96</v>
       </c>
       <c r="E322" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F322" t="n">
-        <v>178</v>
+        <v>658</v>
       </c>
       <c r="G322" t="n">
         <v>0</v>
@@ -9464,22 +9452,22 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(1)-Exact-SP</t>
+          <t>Skadio B0BPPNQYX4-AT</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0BPPNQYX4</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F323" t="n">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="G323" t="n">
         <v>0</v>
@@ -9492,12 +9480,12 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(11)-SP-Exact</t>
+          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -9507,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="F324" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -9520,419 +9508,27 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
+          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>338.2</v>
+        <v>19.5</v>
       </c>
       <c r="E325" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F325" t="n">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr"/>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-SP-Exact</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D326" t="n">
-        <v>0</v>
-      </c>
-      <c r="E326" t="n">
-        <v>0</v>
-      </c>
-      <c r="F326" t="n">
-        <v>2</v>
-      </c>
-      <c r="G326" t="n">
-        <v>0</v>
-      </c>
-      <c r="H326" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr"/>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D327" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="E327" t="n">
-        <v>2</v>
-      </c>
-      <c r="F327" t="n">
-        <v>47</v>
-      </c>
-      <c r="G327" t="n">
-        <v>0</v>
-      </c>
-      <c r="H327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr"/>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner/-B0F43P6D23-HG Exact(1)-SP</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D328" t="n">
-        <v>0</v>
-      </c>
-      <c r="E328" t="n">
-        <v>0</v>
-      </c>
-      <c r="F328" t="n">
-        <v>4</v>
-      </c>
-      <c r="G328" t="n">
-        <v>0</v>
-      </c>
-      <c r="H328" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr"/>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D329" t="n">
-        <v>0</v>
-      </c>
-      <c r="E329" t="n">
-        <v>0</v>
-      </c>
-      <c r="F329" t="n">
-        <v>0</v>
-      </c>
-      <c r="G329" t="n">
-        <v>0</v>
-      </c>
-      <c r="H329" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr"/>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D330" t="n">
-        <v>0</v>
-      </c>
-      <c r="E330" t="n">
-        <v>0</v>
-      </c>
-      <c r="F330" t="n">
-        <v>14</v>
-      </c>
-      <c r="G330" t="n">
-        <v>0</v>
-      </c>
-      <c r="H330" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr"/>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Mop Floor-B0DNJS23HS-BM-KW(1)-SP</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D331" t="n">
-        <v>0</v>
-      </c>
-      <c r="E331" t="n">
-        <v>0</v>
-      </c>
-      <c r="F331" t="n">
-        <v>8</v>
-      </c>
-      <c r="G331" t="n">
-        <v>0</v>
-      </c>
-      <c r="H331" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr"/>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Nexliv-steam cleaner for kitchen -KW(3)-BM-SP</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D332" t="n">
-        <v>104.33</v>
-      </c>
-      <c r="E332" t="n">
-        <v>5</v>
-      </c>
-      <c r="F332" t="n">
-        <v>23</v>
-      </c>
-      <c r="G332" t="n">
-        <v>0</v>
-      </c>
-      <c r="H332" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr"/>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Nexlive Steam Cleaner-B0F43P6D23-KW(1)BM-SP</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D333" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="E333" t="n">
-        <v>1</v>
-      </c>
-      <c r="F333" t="n">
-        <v>7</v>
-      </c>
-      <c r="G333" t="n">
-        <v>0</v>
-      </c>
-      <c r="H333" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr"/>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-BM-SP</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D334" t="n">
-        <v>911.54</v>
-      </c>
-      <c r="E334" t="n">
-        <v>78</v>
-      </c>
-      <c r="F334" t="n">
-        <v>10457</v>
-      </c>
-      <c r="G334" t="n">
-        <v>0</v>
-      </c>
-      <c r="H334" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr"/>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D335" t="n">
-        <v>457.8</v>
-      </c>
-      <c r="E335" t="n">
-        <v>45</v>
-      </c>
-      <c r="F335" t="n">
-        <v>9062</v>
-      </c>
-      <c r="G335" t="n">
-        <v>0</v>
-      </c>
-      <c r="H335" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Nexlive-Portable Cordless Lint Remover-B0FT8R24QM-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>B0FT8R24QM</t>
-        </is>
-      </c>
-      <c r="D336" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="E336" t="n">
-        <v>2</v>
-      </c>
-      <c r="F336" t="n">
-        <v>658</v>
-      </c>
-      <c r="G336" t="n">
-        <v>0</v>
-      </c>
-      <c r="H336" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr"/>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Skadio B0BPPNQYX4-AT</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>B0BPPNQYX4</t>
-        </is>
-      </c>
-      <c r="D337" t="n">
-        <v>6</v>
-      </c>
-      <c r="E337" t="n">
-        <v>1</v>
-      </c>
-      <c r="F337" t="n">
-        <v>114</v>
-      </c>
-      <c r="G337" t="n">
-        <v>0</v>
-      </c>
-      <c r="H337" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr"/>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
-      <c r="D338" t="n">
-        <v>0</v>
-      </c>
-      <c r="E338" t="n">
-        <v>0</v>
-      </c>
-      <c r="F338" t="n">
-        <v>15</v>
-      </c>
-      <c r="G338" t="n">
-        <v>0</v>
-      </c>
-      <c r="H338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr"/>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D339" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E339" t="n">
-        <v>1</v>
-      </c>
-      <c r="F339" t="n">
-        <v>15</v>
-      </c>
-      <c r="G339" t="n">
-        <v>0</v>
-      </c>
-      <c r="H339" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9951,42 +9547,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -11153,13 +10749,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>268.68</v>
+        <v>208.89</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>4835</v>
+        <v>4532</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -11181,13 +10777,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>813.3099999999999</v>
+        <v>716.5699999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F44" t="n">
-        <v>19593</v>
+        <v>17267</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -11209,13 +10805,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>230.65</v>
+        <v>187.41</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
-        <v>4010</v>
+        <v>2865</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -11237,13 +10833,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>249.83</v>
+        <v>163.2</v>
       </c>
       <c r="E46" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F46" t="n">
-        <v>3612</v>
+        <v>2873</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -11265,13 +10861,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>66.09</v>
+        <v>6.59</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1725</v>
+        <v>1401</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -11491,47 +11087,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -1627,7 +1627,7 @@
         <v>68</v>
       </c>
       <c r="F43" t="n">
-        <v>16173</v>
+        <v>16170</v>
       </c>
       <c r="G43" t="n">
         <v>668.64</v>
@@ -1683,7 +1683,7 @@
         <v>539</v>
       </c>
       <c r="F45" t="n">
-        <v>51770</v>
+        <v>51768</v>
       </c>
       <c r="G45" t="n">
         <v>54172.85</v>
@@ -1767,7 +1767,7 @@
         <v>233</v>
       </c>
       <c r="F48" t="n">
-        <v>10251</v>
+        <v>10250</v>
       </c>
       <c r="G48" t="n">
         <v>3388.98</v>
@@ -1879,7 +1879,7 @@
         <v>56</v>
       </c>
       <c r="F52" t="n">
-        <v>6884</v>
+        <v>6883</v>
       </c>
       <c r="G52" t="n">
         <v>4806.780000000001</v>
@@ -1963,7 +1963,7 @@
         <v>33</v>
       </c>
       <c r="F55" t="n">
-        <v>13088</v>
+        <v>13084</v>
       </c>
       <c r="G55" t="n">
         <v>3542.35</v>
@@ -2103,7 +2103,7 @@
         <v>136</v>
       </c>
       <c r="F60" t="n">
-        <v>32320</v>
+        <v>32318</v>
       </c>
       <c r="G60" t="n">
         <v>4517.8</v>
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3071.23</v>
+        <v>3063.96</v>
       </c>
       <c r="E63" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F63" t="n">
-        <v>75110</v>
+        <v>75105</v>
       </c>
       <c r="G63" t="n">
         <v>5083.9</v>
@@ -2271,7 +2271,7 @@
         <v>107</v>
       </c>
       <c r="F66" t="n">
-        <v>26862</v>
+        <v>26860</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>117</v>
       </c>
       <c r="F67" t="n">
-        <v>9500</v>
+        <v>9499</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>16</v>
       </c>
       <c r="F71" t="n">
-        <v>5619</v>
+        <v>5618</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>46.05</v>
+        <v>34.33</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>127</v>
       </c>
       <c r="F75" t="n">
-        <v>14326</v>
+        <v>14325</v>
       </c>
       <c r="G75" t="n">
         <v>24997.14</v>
@@ -2607,7 +2607,7 @@
         <v>114</v>
       </c>
       <c r="F78" t="n">
-        <v>14663</v>
+        <v>14661</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>7221</v>
+        <v>7220</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="F84" t="n">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G84" t="n">
         <v>856.1900000000001</v>
@@ -2803,7 +2803,7 @@
         <v>147</v>
       </c>
       <c r="F85" t="n">
-        <v>27278</v>
+        <v>27276</v>
       </c>
       <c r="G85" t="n">
         <v>30333.9</v>
@@ -2859,7 +2859,7 @@
         <v>35</v>
       </c>
       <c r="F87" t="n">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>126</v>
       </c>
       <c r="F88" t="n">
-        <v>38055</v>
+        <v>38053</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>210</v>
       </c>
       <c r="F89" t="n">
-        <v>13254</v>
+        <v>13251</v>
       </c>
       <c r="G89" t="n">
         <v>10462.7</v>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3913.74</v>
+        <v>3910.63</v>
       </c>
       <c r="E95" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F95" t="n">
-        <v>111755</v>
+        <v>111747</v>
       </c>
       <c r="G95" t="n">
         <v>6099.16</v>
@@ -3139,7 +3139,7 @@
         <v>71</v>
       </c>
       <c r="F97" t="n">
-        <v>31960</v>
+        <v>31951</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>8</v>
       </c>
       <c r="F115" t="n">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>17</v>
       </c>
       <c r="F116" t="n">
-        <v>4948</v>
+        <v>4945</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>71</v>
       </c>
       <c r="F117" t="n">
-        <v>32188</v>
+        <v>32186</v>
       </c>
       <c r="G117" t="n">
         <v>2879.66</v>
@@ -4035,7 +4035,7 @@
         <v>38</v>
       </c>
       <c r="F129" t="n">
-        <v>7315</v>
+        <v>7313</v>
       </c>
       <c r="G129" t="n">
         <v>1238.98</v>
@@ -4063,7 +4063,7 @@
         <v>58</v>
       </c>
       <c r="F130" t="n">
-        <v>11426</v>
+        <v>11423</v>
       </c>
       <c r="G130" t="n">
         <v>3551.7</v>
@@ -4147,7 +4147,7 @@
         <v>59</v>
       </c>
       <c r="F133" t="n">
-        <v>5761</v>
+        <v>5760</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
         <v>49</v>
       </c>
       <c r="F135" t="n">
-        <v>5463</v>
+        <v>5462</v>
       </c>
       <c r="G135" t="n">
         <v>2093.34</v>
@@ -4315,7 +4315,7 @@
         <v>92</v>
       </c>
       <c r="F139" t="n">
-        <v>32781</v>
+        <v>32778</v>
       </c>
       <c r="G139" t="n">
         <v>4312.71</v>
@@ -4511,7 +4511,7 @@
         <v>92</v>
       </c>
       <c r="F146" t="n">
-        <v>7724</v>
+        <v>7723</v>
       </c>
       <c r="G146" t="n">
         <v>7236.2</v>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1302.64</v>
+        <v>1269.68</v>
       </c>
       <c r="E153" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F153" t="n">
-        <v>19947</v>
+        <v>19935</v>
       </c>
       <c r="G153" t="n">
         <v>5209.32</v>
@@ -4735,7 +4735,7 @@
         <v>205</v>
       </c>
       <c r="F154" t="n">
-        <v>39114</v>
+        <v>39105</v>
       </c>
       <c r="G154" t="n">
         <v>6920.34</v>
@@ -4791,7 +4791,7 @@
         <v>91</v>
       </c>
       <c r="F156" t="n">
-        <v>17068</v>
+        <v>17063</v>
       </c>
       <c r="G156" t="n">
         <v>5099.15</v>
@@ -4959,7 +4959,7 @@
         <v>322</v>
       </c>
       <c r="F162" t="n">
-        <v>157697</v>
+        <v>157690</v>
       </c>
       <c r="G162" t="n">
         <v>14209.32</v>
@@ -4987,7 +4987,7 @@
         <v>50</v>
       </c>
       <c r="F163" t="n">
-        <v>15173</v>
+        <v>15169</v>
       </c>
       <c r="G163" t="n">
         <v>6099.15</v>
@@ -5015,7 +5015,7 @@
         <v>24</v>
       </c>
       <c r="F164" t="n">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>34</v>
       </c>
       <c r="F165" t="n">
-        <v>5675</v>
+        <v>5670</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -10749,13 +10749,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>208.89</v>
+        <v>201.86</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>4532</v>
+        <v>4525</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H325"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,40 +464,40 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Campaign - 20/5/2026 16:32:01.948</t>
+          <t>HnK_SP_KT_SS-01/SS-02 - Type A (Brand Analytic)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>306.36</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4099</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8048.309999999999</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HnK_SP_KT_SS-01/SS-02 - Type A (Brand Analytic)</t>
+          <t>HnK_SP_KT_VC-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -520,12 +520,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HnK_SP_KT_VC-02</t>
+          <t>Nex_HPC_SP_Auto_KM-01_B0DM66B2DW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -548,12 +548,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_Auto_KM-01_B0DM66B2DW</t>
+          <t>Nex_HPC_SP_CT_V-03_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -576,12 +576,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_CT_FS-01_B0D9KFZYG8</t>
+          <t>Nex_HPC_SP_KT_HSB-03_B0D9KFP4MG_MV_Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -604,7 +604,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_CT_V-03_B0DQCWRG3H</t>
+          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -632,12 +632,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_EA-01_B0D67727VG_Exact</t>
+          <t>Nex_HPC_SP_KT_V-03_Comp_B0DQCWRG3H_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -660,12 +660,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_HSB-03_B0D9KFP4MG_MV_Exact</t>
+          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -688,12 +688,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-01_CVR_Exact</t>
+          <t>Nex_HnK_SP_CT_(SM-01)_Wet &amp; Dry Mops</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -716,12 +716,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_CG_LV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_CT_SC-01_B0CDPP45BM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -744,12 +744,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_MV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -772,12 +772,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_Comp_B0DQCWRG3H_HV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_AP-04_B0GN8N96R5_Gen_Exact_HV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -800,12 +800,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_PT_CFM-01_B0DM6BB3VT</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_BCG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -828,12 +828,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -856,12 +856,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_(SM-01)_Wet &amp; Dry Mops</t>
+          <t>Nex_HnK_SP_KT_LR-02_B0D845B2DG_LV_Exact_Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -884,12 +884,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_GS-02_B0CDPMX152</t>
+          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -912,7 +912,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_SC-01_B0CDPP45BM</t>
+          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Gen_HV_Exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -940,12 +940,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_GS-02_B0CDPMX152</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -968,12 +968,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
+          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -996,12 +996,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_AP-04_B0GN8N96R5_Gen_Exact_HV</t>
+          <t>Nex_HnK_SP|SS-02-B0DNJP9T35| Auto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1024,7 +1024,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_CAP-05_B0GN86G345_Gen_HV_Phrase</t>
+          <t>Nex_Hnk_SP_Auto_CAP-05_B0GN86G345</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1052,12 +1052,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_CG_MV_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SP_PT - MC-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1080,12 +1080,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_Gen_Phrase_HV</t>
+          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1108,22 +1108,22 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_BCG</t>
+          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>271.16</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>7727</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1136,124 +1136,124 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>6277.82</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>23164</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>40350.82</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_LR-02_B0D845B2DG_LV_Exact_Phrase</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1428.37</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>11861.86</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4123.32</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>5839</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>15504.22</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_CG_LV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2815.03</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>7391</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-02_B0DCK7ZH5P_Gen_HV_Phrase</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1276,68 +1276,68 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Gen_HV_Exact</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>314.3</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2765</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3261.02</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
+          <t>Nexlev - B0D63FKYZ5 - Scalp Massager - Broad</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>270.62</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>5297</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>951.4299999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Phrase</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1360,50 +1360,50 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>227.09</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5913</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3542.35</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_CG_MV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>655.96</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>13973</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,22 +1416,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>319.49</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>6135</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,22 +1444,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP|SS-02-B0DNJP9T35| Auto</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>68.16</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>6864</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,22 +1472,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_Auto_CAP-05_B0GN86G345</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>228.14</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,50 +1500,50 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_KT - MC-01</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1101.34</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>28946</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1295.76</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_KT_ST-02_B0GN94YDY2_CG_MV_Phrase &amp; Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>396.76</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2509</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,12 +1556,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT - MC-01</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1584,78 +1584,78 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2070.91</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>45952</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>501.05</v>
+        <v>741.49</v>
       </c>
       <c r="E43" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F43" t="n">
-        <v>16170</v>
+        <v>1495</v>
       </c>
       <c r="G43" t="n">
-        <v>668.64</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPMX152 - Handheld Garment Steamer - KT - Comp - Multi Ad Group 07</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>992.65</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>5076</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,134 +1668,134 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8066.38</v>
+        <v>1202.93</v>
       </c>
       <c r="E45" t="n">
-        <v>539</v>
+        <v>79</v>
       </c>
       <c r="F45" t="n">
-        <v>51768</v>
+        <v>22365</v>
       </c>
       <c r="G45" t="n">
-        <v>54172.85</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2013.19</v>
+        <v>1205.95</v>
       </c>
       <c r="E46" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="F46" t="n">
-        <v>8239</v>
+        <v>4696</v>
       </c>
       <c r="G46" t="n">
-        <v>11861.86</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5684.54</v>
+        <v>9.9</v>
       </c>
       <c r="E47" t="n">
-        <v>458</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>7779</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>25671.16</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Exact</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3605.5</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>10250</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev - B0CYSLCRQS - Sofa &amp; Carpet Vacuum Cleaner - KT - Exact11</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>195.84</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>6789</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,12 +1808,12 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB -  Foldable Garment Steamer 0 - SP - PT</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1836,22 +1836,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>221.76</v>
+        <v>1331.89</v>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F51" t="n">
-        <v>17379</v>
+        <v>4791</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,134 +1864,134 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>938.5600000000001</v>
+        <v>1960.46</v>
       </c>
       <c r="E52" t="n">
         <v>56</v>
       </c>
       <c r="F52" t="n">
-        <v>6883</v>
+        <v>4018</v>
       </c>
       <c r="G52" t="n">
-        <v>4806.780000000001</v>
+        <v>14090.49</v>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev - B0D63FKYZ5 - Scalp Massager - Broad</t>
+          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>348.19</v>
+        <v>81.48</v>
       </c>
       <c r="E53" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>7655</v>
+        <v>3810</v>
       </c>
       <c r="G53" t="n">
-        <v>951.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2175.57</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>15844</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>456.61</v>
+        <v>1377.28</v>
       </c>
       <c r="E55" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F55" t="n">
-        <v>13084</v>
+        <v>9758</v>
       </c>
       <c r="G55" t="n">
-        <v>3542.35</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>730.4400000000001</v>
+        <v>1158.06</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F56" t="n">
-        <v>14542</v>
+        <v>4427</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,50 +2004,50 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>548.5599999999999</v>
+        <v>1314.32</v>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F57" t="n">
-        <v>9127</v>
+        <v>1049</v>
       </c>
       <c r="G57" t="n">
-        <v>2116.94</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>68.16</v>
+        <v>869.6799999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F58" t="n">
-        <v>6864</v>
+        <v>25567</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
+          <t>Nexlev - B0DQCWRG3H - Ionic 3 in 1 Hot Air Brush - Broad1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>228.14</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,68 +2088,68 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - BM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1279.7</v>
+        <v>36.12</v>
       </c>
       <c r="E60" t="n">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>32318</v>
+        <v>297</v>
       </c>
       <c r="G60" t="n">
-        <v>4517.8</v>
+        <v>856.1900000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>396.76</v>
+        <v>1188.09</v>
       </c>
       <c r="E61" t="n">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="F61" t="n">
-        <v>2509</v>
+        <v>19938</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
+          <t>Nexlev - B0DVC8NYY2 -  Ultrasonic Cool Mist Humidifier - KT - Excat 00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2172,106 +2172,106 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3063.96</v>
+        <v>279.27</v>
       </c>
       <c r="E63" t="n">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>75105</v>
+        <v>1813</v>
       </c>
       <c r="G63" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1581.34</v>
+        <v>1131.54</v>
       </c>
       <c r="E64" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="F64" t="n">
-        <v>7487</v>
+        <v>21399</v>
       </c>
       <c r="G64" t="n">
-        <v>2826.27</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1811.91</v>
+        <v>2021.55</v>
       </c>
       <c r="E65" t="n">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="F65" t="n">
-        <v>7773</v>
+        <v>8384</v>
       </c>
       <c r="G65" t="n">
-        <v>2826.27</v>
+        <v>8005.92</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1602.07</v>
+        <v>543.34</v>
       </c>
       <c r="E66" t="n">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="F66" t="n">
-        <v>26860</v>
+        <v>2153</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,22 +2284,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2025.73</v>
+        <v>939.8</v>
       </c>
       <c r="E67" t="n">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="F67" t="n">
-        <v>9499</v>
+        <v>21222</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,50 +2312,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>254.56</v>
+        <v>6969.53</v>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>344</v>
       </c>
       <c r="F68" t="n">
-        <v>7193</v>
+        <v>33492</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>23764.38</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Exact</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner 01 - KT - Branded - Phrase - Exact</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>135.56</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>3316</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,78 +2368,78 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>244.83</v>
+        <v>2820.96</v>
       </c>
       <c r="E70" t="n">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="F70" t="n">
-        <v>10009</v>
+        <v>87189</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>6099.16</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - BM</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>178.44</v>
+        <v>1600.58</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="F71" t="n">
-        <v>5618</v>
+        <v>23749</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>6099.15</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - Exact</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>34.33</v>
+        <v>501.29</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F72" t="n">
-        <v>669</v>
+        <v>13053</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,50 +2452,50 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - PT</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1142.09</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>3474</v>
+        <v>173</v>
       </c>
       <c r="G73" t="n">
-        <v>1719.5</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2260.02</v>
+        <v>7.3</v>
       </c>
       <c r="E74" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>8060</v>
+        <v>29</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2508,218 +2508,218 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nexlev - Stand Mixer - SP - CT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4426.690000000001</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>14325</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>24997.14</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>158.16</v>
+        <v>4987.32</v>
       </c>
       <c r="E76" t="n">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="F76" t="n">
-        <v>6823</v>
+        <v>12790</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>9446.6</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2830.91</v>
+        <v>857.52</v>
       </c>
       <c r="E77" t="n">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="F77" t="n">
-        <v>24021</v>
+        <v>1961</v>
       </c>
       <c r="G77" t="n">
-        <v>10167.8</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1924.39</v>
+        <v>956.04</v>
       </c>
       <c r="E78" t="n">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="F78" t="n">
-        <v>14661</v>
+        <v>4223</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1659.48</v>
+        <v>822.23</v>
       </c>
       <c r="E79" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F79" t="n">
-        <v>7220</v>
+        <v>1771</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
+          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1980.39</v>
+        <v>332.46</v>
       </c>
       <c r="E80" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F80" t="n">
-        <v>1343</v>
+        <v>1123</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>619.49</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
+          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1522.36</v>
+        <v>642.13</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>36461</v>
+        <v>1595</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1439.83</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev - B0DQCWRG3H - Ionic 3 in 1 Hot Air Brush - Broad1</t>
+          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>899.73</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1489</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2732,22 +2732,22 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>72.04000000000001</v>
+        <v>839.6</v>
       </c>
       <c r="E83" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F83" t="n">
-        <v>7783</v>
+        <v>1076</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2760,106 +2760,106 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - BM</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>83.09</v>
+        <v>6016.32</v>
       </c>
       <c r="E84" t="n">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="F84" t="n">
-        <v>598</v>
+        <v>29894</v>
       </c>
       <c r="G84" t="n">
-        <v>856.1900000000001</v>
+        <v>24060.14</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1663.11</v>
+        <v>2289.71</v>
       </c>
       <c r="E85" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="F85" t="n">
-        <v>27276</v>
+        <v>2223</v>
       </c>
       <c r="G85" t="n">
-        <v>30333.9</v>
+        <v>8048.299999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC8NYY2 -  Ultrasonic Cool Mist Humidifier - KT - Excat 00</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>120.93</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>4236.44</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>664.73</v>
+        <v>116.57</v>
       </c>
       <c r="E87" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F87" t="n">
-        <v>2826</v>
+        <v>2070</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,22 +2872,22 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1966.49</v>
+        <v>114.04</v>
       </c>
       <c r="E88" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>38053</v>
+        <v>725</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,162 +2900,162 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2925.08</v>
+        <v>155.63</v>
       </c>
       <c r="E89" t="n">
-        <v>210</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
-        <v>13251</v>
+        <v>3046</v>
       </c>
       <c r="G89" t="n">
-        <v>10462.7</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - KT - Comp - Multi Ad Group - 01</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>552.41</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>20997</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1439.83</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1077.96</v>
+        <v>154.54</v>
       </c>
       <c r="E91" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
-        <v>4002</v>
+        <v>498</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1270.34</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1573.99</v>
+        <v>94.27</v>
       </c>
       <c r="E92" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>41752</v>
+        <v>1148</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1608.48</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>9109.17</v>
+        <v>5.86</v>
       </c>
       <c r="E93" t="n">
-        <v>447</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>45542</v>
+        <v>62</v>
       </c>
       <c r="G93" t="n">
-        <v>32490.64</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner 01 - KT - Branded - Phrase - Exact</t>
+          <t>Nexlev-B0CDPMX152-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>64.16</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,78 +3068,78 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3910.63</v>
+        <v>1618.44</v>
       </c>
       <c r="E95" t="n">
-        <v>287</v>
+        <v>153</v>
       </c>
       <c r="F95" t="n">
-        <v>111747</v>
+        <v>5867</v>
       </c>
       <c r="G95" t="n">
-        <v>6099.16</v>
+        <v>3388.98</v>
       </c>
       <c r="H95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2300.22</v>
+        <v>1513.58</v>
       </c>
       <c r="E96" t="n">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>33784</v>
+        <v>7597</v>
       </c>
       <c r="G96" t="n">
-        <v>8132.21</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>990.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>31951</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3152,22 +3152,22 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN86G345 -  Car Air Purifier - KT - Multi Ad Group</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>955.71</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>4014</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3180,22 +3180,22 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>938.45</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F99" t="n">
-        <v>173</v>
+        <v>7355</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3208,22 +3208,22 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7.3</v>
+        <v>880.5</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="F100" t="n">
-        <v>29</v>
+        <v>3413</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,106 +3236,106 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev - Stand Mixer - SP - CT</t>
+          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>233.49</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>4224</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>619.49</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPMX152- Garment Steamer -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>279.64</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>6301</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2932.21</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6775.78</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>18152</v>
+        <v>29</v>
       </c>
       <c r="G103" t="n">
-        <v>12835.58</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1318.11</v>
+        <v>13.39</v>
       </c>
       <c r="E104" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>2999</v>
+        <v>372</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3348,81 +3348,81 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1315.53</v>
+        <v>490.22</v>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F105" t="n">
-        <v>6697</v>
+        <v>798</v>
       </c>
       <c r="G105" t="n">
-        <v>338.14</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1188.01</v>
+        <v>126.67</v>
       </c>
       <c r="E106" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="F106" t="n">
-        <v>2335</v>
+        <v>64</v>
       </c>
       <c r="G106" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>528.23</v>
+        <v>285.04</v>
       </c>
       <c r="E107" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F107" t="n">
-        <v>2432</v>
+        <v>3462</v>
       </c>
       <c r="G107" t="n">
-        <v>619.49</v>
+        <v>1046.67</v>
       </c>
       <c r="H107" t="n">
         <v>1</v>
@@ -3432,50 +3432,50 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>936.26</v>
+        <v>46.46</v>
       </c>
       <c r="E108" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>2302</v>
+        <v>136</v>
       </c>
       <c r="G108" t="n">
-        <v>1439.83</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-Auto</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1446.1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>2566</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,22 +3488,22 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1208</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>1550</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3516,162 +3516,162 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8444.370000000001</v>
+        <v>1410.3</v>
       </c>
       <c r="E111" t="n">
-        <v>785</v>
+        <v>68</v>
       </c>
       <c r="F111" t="n">
-        <v>45089</v>
+        <v>22537</v>
       </c>
       <c r="G111" t="n">
-        <v>45095.72</v>
+        <v>2879.66</v>
       </c>
       <c r="H111" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3209.32</v>
+        <v>431.85</v>
       </c>
       <c r="E112" t="n">
-        <v>226</v>
+        <v>23</v>
       </c>
       <c r="F112" t="n">
-        <v>3076</v>
+        <v>8714</v>
       </c>
       <c r="G112" t="n">
-        <v>8048.299999999999</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>161.27</v>
+        <v>166.61</v>
       </c>
       <c r="E113" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>1387</v>
+        <v>687</v>
       </c>
       <c r="G113" t="n">
-        <v>6902.15</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>199.01</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F114" t="n">
-        <v>2864</v>
+        <v>649</v>
       </c>
       <c r="G114" t="n">
-        <v>6608.48</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>149.75</v>
+        <v>1284.69</v>
       </c>
       <c r="E115" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F115" t="n">
-        <v>1211</v>
+        <v>10440</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>286.08</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>4945</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3684,106 +3684,106 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1083.94</v>
+        <v>624.3299999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="F117" t="n">
-        <v>32186</v>
+        <v>685</v>
       </c>
       <c r="G117" t="n">
-        <v>2879.66</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>365.92</v>
+        <v>494.03</v>
       </c>
       <c r="E118" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>994</v>
+        <v>5086</v>
       </c>
       <c r="G118" t="n">
-        <v>1270.34</v>
+        <v>5351.43</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>225.07</v>
+        <v>639.71</v>
       </c>
       <c r="E119" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F119" t="n">
-        <v>2322</v>
+        <v>1427</v>
       </c>
       <c r="G119" t="n">
-        <v>4062.72</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev-B0DNJP9T35-Spin Scrubber- SP -KT-Phrase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3796,53 +3796,53 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>70.78</v>
+        <v>2207.18</v>
       </c>
       <c r="E121" t="n">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="F121" t="n">
-        <v>1103</v>
+        <v>18507</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2892.06</v>
+        <v>1035.69</v>
       </c>
       <c r="E122" t="n">
-        <v>232</v>
+        <v>68</v>
       </c>
       <c r="F122" t="n">
-        <v>10314</v>
+        <v>2051</v>
       </c>
       <c r="G122" t="n">
-        <v>3388.98</v>
+        <v>5083.9</v>
       </c>
       <c r="H122" t="n">
         <v>1</v>
@@ -3852,22 +3852,22 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2392.24</v>
+        <v>621.33</v>
       </c>
       <c r="E123" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>14138</v>
+        <v>817</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3880,22 +3880,22 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>1880.62</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>3970</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3908,78 +3908,78 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1268.02</v>
+        <v>743.8</v>
       </c>
       <c r="E125" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F125" t="n">
-        <v>5676</v>
+        <v>10894</v>
       </c>
       <c r="G125" t="n">
-        <v>2456.78</v>
+        <v>5209.32</v>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1427.93</v>
+        <v>1502.43</v>
       </c>
       <c r="E126" t="n">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="F126" t="n">
-        <v>10126</v>
+        <v>26778</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>5209.32</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>251.75</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>12055</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3992,22 +3992,22 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1271.1</v>
+        <v>634.54</v>
       </c>
       <c r="E128" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="F128" t="n">
-        <v>5548</v>
+        <v>8412</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4020,106 +4020,106 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>464.74</v>
+        <v>406.53</v>
       </c>
       <c r="E129" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F129" t="n">
-        <v>7313</v>
+        <v>2001</v>
       </c>
       <c r="G129" t="n">
-        <v>1238.98</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>556.7</v>
+        <v>2729.26</v>
       </c>
       <c r="E130" t="n">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="F130" t="n">
-        <v>11423</v>
+        <v>5902</v>
       </c>
       <c r="G130" t="n">
-        <v>3551.7</v>
+        <v>9996.610000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>160.44</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>3197.46</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>13.39</v>
+        <v>154.98</v>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F132" t="n">
-        <v>517</v>
+        <v>1040</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4132,106 +4132,106 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1956.25</v>
+        <v>3779.3</v>
       </c>
       <c r="E133" t="n">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="F133" t="n">
-        <v>5760</v>
+        <v>10460</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>14106.77</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>266.56</v>
+        <v>3355.44</v>
       </c>
       <c r="E134" t="n">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="F134" t="n">
-        <v>207</v>
+        <v>129842</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>12198.3</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>464.45</v>
+        <v>156.96</v>
       </c>
       <c r="E135" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F135" t="n">
-        <v>5462</v>
+        <v>9789</v>
       </c>
       <c r="G135" t="n">
-        <v>2093.34</v>
+        <v>4066.1</v>
       </c>
       <c r="H135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>57.27</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4244,22 +4244,22 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nexlev-B0D845B2DG-Lint Remover-SP-Auto</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>159.42</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>3625</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4272,22 +4272,22 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>23.35</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4300,50 +4300,50 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1994.63</v>
+        <v>40.87</v>
       </c>
       <c r="E139" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="F139" t="n">
-        <v>32778</v>
+        <v>3311</v>
       </c>
       <c r="G139" t="n">
-        <v>4312.71</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>726.0599999999999</v>
+        <v>19.31</v>
       </c>
       <c r="E140" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="F140" t="n">
-        <v>11808</v>
+        <v>2343</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4356,22 +4356,22 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>569.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>3605</v>
+        <v>55</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4384,22 +4384,22 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>149.8</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>913</v>
+        <v>23</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4412,25 +4412,25 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1874.23</v>
+        <v>13.2</v>
       </c>
       <c r="E143" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="F143" t="n">
-        <v>12555</v>
+        <v>1144</v>
       </c>
       <c r="G143" t="n">
-        <v>2541.53</v>
+        <v>677.12</v>
       </c>
       <c r="H143" t="n">
         <v>1</v>
@@ -4440,22 +4440,22 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4468,22 +4468,22 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1121.73</v>
+        <v>10.2</v>
       </c>
       <c r="E145" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>1437</v>
+        <v>80</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4496,78 +4496,78 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>851.7</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>7723</v>
+        <v>18</v>
       </c>
       <c r="G146" t="n">
-        <v>7236.2</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1077.5</v>
+        <v>14.9</v>
       </c>
       <c r="E147" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>2660</v>
+        <v>86</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1295.76</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJP9T35-Spin Scrubber- SP -KT-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>21.14</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1159</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4580,78 +4580,78 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3154.81</v>
+        <v>13.33</v>
       </c>
       <c r="E149" t="n">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
-        <v>28854</v>
+        <v>51</v>
       </c>
       <c r="G149" t="n">
-        <v>17200</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1259.88</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>3001</v>
+        <v>61</v>
       </c>
       <c r="G150" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>697.29</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>1759</v>
+        <v>59</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4664,22 +4664,22 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2720.39</v>
+        <v>13.6</v>
       </c>
       <c r="E152" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="F152" t="n">
-        <v>8554</v>
+        <v>479</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4692,78 +4692,78 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1269.68</v>
+        <v>6.8</v>
       </c>
       <c r="E153" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>19935</v>
+        <v>366</v>
       </c>
       <c r="G153" t="n">
-        <v>5209.32</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2135.97</v>
+        <v>30.89</v>
       </c>
       <c r="E154" t="n">
-        <v>205</v>
+        <v>5</v>
       </c>
       <c r="F154" t="n">
-        <v>39105</v>
+        <v>496</v>
       </c>
       <c r="G154" t="n">
-        <v>6920.34</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>306.73</v>
+        <v>58.25</v>
       </c>
       <c r="E155" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="F155" t="n">
-        <v>16152</v>
+        <v>354</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4776,96 +4776,96 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1488.64</v>
+        <v>6.22</v>
       </c>
       <c r="E156" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>17063</v>
+        <v>243</v>
       </c>
       <c r="G156" t="n">
-        <v>5099.15</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>513.51</v>
+        <v>31.38</v>
       </c>
       <c r="E157" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F157" t="n">
-        <v>3139</v>
+        <v>805</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1778.81</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4065.9</v>
+        <v>40.5</v>
       </c>
       <c r="E158" t="n">
-        <v>203</v>
+        <v>9</v>
       </c>
       <c r="F158" t="n">
-        <v>9739</v>
+        <v>444</v>
       </c>
       <c r="G158" t="n">
-        <v>12538.13</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4888,22 +4888,22 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>222</v>
+        <v>6.8</v>
       </c>
       <c r="E160" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
-        <v>1479</v>
+        <v>6</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4916,106 +4916,106 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5026.36</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>14305</v>
+        <v>5</v>
       </c>
       <c r="G161" t="n">
-        <v>16775.41</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4213.450000000001</v>
+        <v>21.89</v>
       </c>
       <c r="E162" t="n">
-        <v>322</v>
+        <v>7</v>
       </c>
       <c r="F162" t="n">
-        <v>157690</v>
+        <v>48</v>
       </c>
       <c r="G162" t="n">
-        <v>14209.32</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>245.7</v>
+        <v>107.07</v>
       </c>
       <c r="E163" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F163" t="n">
-        <v>15169</v>
+        <v>2509</v>
       </c>
       <c r="G163" t="n">
-        <v>6099.15</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>408.59</v>
+        <v>9.33</v>
       </c>
       <c r="E164" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F164" t="n">
-        <v>3467</v>
+        <v>229</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5028,22 +5028,22 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>372.84</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>5670</v>
+        <v>82</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>40.87</v>
+        <v>13.6</v>
       </c>
       <c r="E167" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F167" t="n">
-        <v>3311</v>
+        <v>59</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -5117,17 +5117,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>19.31</v>
+        <v>6.19</v>
       </c>
       <c r="E168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>2343</v>
+        <v>45</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>17.74</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F169" t="n">
-        <v>55</v>
+        <v>770</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5201,23 +5201,23 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>1144</v>
+        <v>31</v>
       </c>
       <c r="G171" t="n">
-        <v>677.12</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -5229,17 +5229,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5257,17 +5257,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10.2</v>
+        <v>25.45</v>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F173" t="n">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5285,23 +5285,23 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>18</v>
+        <v>3494</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>2668.64</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -5313,23 +5313,23 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>14.9</v>
+        <v>4.79</v>
       </c>
       <c r="E175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>86</v>
+        <v>512</v>
       </c>
       <c r="G175" t="n">
-        <v>1295.76</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>21.14</v>
+        <v>14.49</v>
       </c>
       <c r="E176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F176" t="n">
-        <v>1159</v>
+        <v>296</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>13.33</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5425,17 +5425,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5453,17 +5453,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>13.6</v>
+        <v>13.1</v>
       </c>
       <c r="E180" t="n">
         <v>2</v>
       </c>
       <c r="F180" t="n">
-        <v>479</v>
+        <v>565</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>366</v>
+        <v>200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5509,17 +5509,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>30.89</v>
+        <v>14.93</v>
       </c>
       <c r="E182" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F182" t="n">
-        <v>496</v>
+        <v>2303</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>58.25</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>354</v>
+        <v>52</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5565,17 +5565,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5593,23 +5593,23 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>31.38</v>
+        <v>6.8</v>
       </c>
       <c r="E185" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>805</v>
+        <v>282</v>
       </c>
       <c r="G185" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>40.5</v>
+        <v>13.5</v>
       </c>
       <c r="E186" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
-        <v>444</v>
+        <v>115</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5677,17 +5677,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>6.8</v>
+        <v>13.47</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" t="n">
-        <v>6</v>
+        <v>1509</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5705,17 +5705,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>75.95</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F189" t="n">
-        <v>5</v>
+        <v>791</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5728,22 +5728,22 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>21.89</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5756,22 +5756,22 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>107.07</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>2509</v>
+        <v>551</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5784,22 +5784,22 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>9.33</v>
+        <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>229</v>
+        <v>973</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5812,12 +5812,12 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5840,22 +5840,22 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>5</v>
+        <v>3005</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5868,22 +5868,22 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>13.6</v>
+        <v>6.68</v>
       </c>
       <c r="E195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F195" t="n">
-        <v>59</v>
+        <v>883</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5896,22 +5896,22 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>6.19</v>
+        <v>1.57</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5924,22 +5924,22 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>17.74</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>770</v>
+        <v>108</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5952,22 +5952,22 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>4</v>
+        <v>410</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5980,22 +5980,22 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>31</v>
+        <v>672</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -6008,22 +6008,22 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F200" t="n">
-        <v>26</v>
+        <v>578</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -6036,22 +6036,22 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>25.45</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>194</v>
+        <v>4764</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6064,50 +6064,50 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>3494</v>
+        <v>306</v>
       </c>
       <c r="G202" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4.79</v>
+        <v>4.23</v>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F203" t="n">
-        <v>512</v>
+        <v>392</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>14.49</v>
+        <v>11.3</v>
       </c>
       <c r="E204" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F204" t="n">
-        <v>296</v>
+        <v>618</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6148,22 +6148,22 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F205" t="n">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6176,12 +6176,12 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6204,22 +6204,22 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5.31</v>
+        <v>3</v>
       </c>
       <c r="E207" t="n">
         <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6232,22 +6232,22 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>565</v>
+        <v>74</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6260,22 +6260,22 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>347.92</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F209" t="n">
-        <v>200</v>
+        <v>12545</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6288,50 +6288,50 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>14.93</v>
+        <v>465.05</v>
       </c>
       <c r="E210" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="F210" t="n">
-        <v>2303</v>
+        <v>18384</v>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
+        <v>1944.07</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>52</v>
+        <v>259</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6344,22 +6344,22 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>14.85</v>
       </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F212" t="n">
-        <v>129</v>
+        <v>1843</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6372,22 +6372,22 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6400,22 +6400,22 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>13.5</v>
+        <v>50.64</v>
       </c>
       <c r="E214" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F214" t="n">
-        <v>115</v>
+        <v>2487</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6428,22 +6428,22 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F215" t="n">
-        <v>54</v>
+        <v>601</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6456,22 +6456,22 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>13.47</v>
+        <v>11.3</v>
       </c>
       <c r="E216" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>1509</v>
+        <v>431</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6484,22 +6484,22 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>75.95</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>791</v>
+        <v>46</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6545,17 +6545,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>551</v>
+        <v>496</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>973</v>
+        <v>530</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6601,17 +6601,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F221" t="n">
-        <v>103</v>
+        <v>1481</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6629,17 +6629,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>3005</v>
+        <v>2</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6657,17 +6657,17 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>6.68</v>
+        <v>2.6</v>
       </c>
       <c r="E223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F223" t="n">
-        <v>884</v>
+        <v>2938</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>314</v>
+        <v>10</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6741,17 +6741,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>8.92</v>
+        <v>5.08</v>
       </c>
       <c r="E226" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F226" t="n">
-        <v>410</v>
+        <v>975</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6769,17 +6769,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="E227" t="n">
         <v>1</v>
       </c>
       <c r="F227" t="n">
-        <v>673</v>
+        <v>151</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6797,17 +6797,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>8.6</v>
+        <v>1.29</v>
       </c>
       <c r="E228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
-        <v>578</v>
+        <v>375</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>4764</v>
+        <v>83</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6853,23 +6853,23 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="E230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F230" t="n">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>211.02</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>4.23</v>
+        <v>5.33</v>
       </c>
       <c r="E231" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F231" t="n">
-        <v>392</v>
+        <v>184</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6909,23 +6909,23 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>11.3</v>
+        <v>49.46</v>
       </c>
       <c r="E232" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F232" t="n">
-        <v>621</v>
+        <v>592</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>211.02</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>7.69</v>
+        <v>2.7</v>
       </c>
       <c r="E233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0</v>
+        <v>24.87</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>163</v>
+        <v>3218</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6993,17 +6993,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>69</v>
+        <v>367</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7021,17 +7021,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F236" t="n">
-        <v>74</v>
+        <v>403</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7049,17 +7049,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>347.92</v>
+        <v>11.79</v>
       </c>
       <c r="E237" t="n">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="F237" t="n">
-        <v>12554</v>
+        <v>1133</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7077,23 +7077,23 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>465.05</v>
+        <v>3</v>
       </c>
       <c r="E238" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>18401</v>
+        <v>363</v>
       </c>
       <c r="G238" t="n">
-        <v>1944.07</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -7105,17 +7105,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1.3</v>
+        <v>8.07</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F239" t="n">
-        <v>259</v>
+        <v>537</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7133,17 +7133,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>14.85</v>
+        <v>4.3</v>
       </c>
       <c r="E240" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F240" t="n">
-        <v>1843</v>
+        <v>1271</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7161,17 +7161,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F241" t="n">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7184,22 +7184,22 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>50.64</v>
+        <v>0</v>
       </c>
       <c r="E242" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>2487</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E243" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>601</v>
+        <v>1</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7240,22 +7240,22 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>11.3</v>
+        <v>2.6</v>
       </c>
       <c r="E244" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F244" t="n">
-        <v>431</v>
+        <v>5</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7268,12 +7268,12 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7296,12 +7296,12 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -7324,22 +7324,22 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
         <v>1</v>
-      </c>
-      <c r="F247" t="n">
-        <v>496</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7352,12 +7352,12 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>530</v>
+        <v>6</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -7380,22 +7380,22 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>1481</v>
+        <v>0</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -7408,12 +7408,12 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -7436,22 +7436,22 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>2938</v>
+        <v>1</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7464,12 +7464,12 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -7479,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -7492,22 +7492,22 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
         <v>1</v>
-      </c>
-      <c r="F253" t="n">
-        <v>27</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="E254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7548,22 +7548,22 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
         <v>1</v>
-      </c>
-      <c r="F255" t="n">
-        <v>151</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7576,22 +7576,22 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
         <v>1</v>
-      </c>
-      <c r="F256" t="n">
-        <v>375</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7604,12 +7604,12 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -7632,50 +7632,50 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>5.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="E258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F258" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>211.02</v>
+        <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="E259" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F259" t="n">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -7688,50 +7688,50 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>49.46</v>
+        <v>4406.93</v>
       </c>
       <c r="E260" t="n">
-        <v>19</v>
+        <v>412</v>
       </c>
       <c r="F260" t="n">
-        <v>592</v>
+        <v>15600</v>
       </c>
       <c r="G260" t="n">
-        <v>211.02</v>
+        <v>23977.1</v>
       </c>
       <c r="H260" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F261" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -7744,22 +7744,22 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Steam Cleaner-B0F43P6D23-KW(3)-SP-Exact</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>24.87</v>
+        <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F262" t="n">
-        <v>3218</v>
+        <v>4</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7772,22 +7772,22 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0</v>
+        <v>16.74</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>367</v>
+        <v>18</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -7800,22 +7800,22 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>6</v>
+        <v>154.83</v>
       </c>
       <c r="E264" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F264" t="n">
-        <v>403</v>
+        <v>2636</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -7828,22 +7828,22 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>11.79</v>
+        <v>23</v>
       </c>
       <c r="E265" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F265" t="n">
-        <v>1134</v>
+        <v>1045</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -7856,50 +7856,50 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>3</v>
+        <v>101.34</v>
       </c>
       <c r="E266" t="n">
+        <v>12</v>
+      </c>
+      <c r="F266" t="n">
+        <v>729</v>
+      </c>
+      <c r="G266" t="n">
+        <v>2668.64</v>
+      </c>
+      <c r="H266" t="n">
         <v>1</v>
-      </c>
-      <c r="F266" t="n">
-        <v>363</v>
-      </c>
-      <c r="G266" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>8.07</v>
+        <v>657.84</v>
       </c>
       <c r="E267" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="F267" t="n">
-        <v>537</v>
+        <v>3933</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -7912,22 +7912,22 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>4.3</v>
+        <v>428.05</v>
       </c>
       <c r="E268" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F268" t="n">
-        <v>1271</v>
+        <v>1464</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -7940,22 +7940,22 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>18.88</v>
+        <v>253.33</v>
       </c>
       <c r="E269" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F269" t="n">
-        <v>383</v>
+        <v>1437</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -7968,22 +7968,22 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>652.8</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>13715</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -8011,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -8024,22 +8024,22 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2.6</v>
+        <v>58.79</v>
       </c>
       <c r="E272" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F272" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -8052,40 +8052,40 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>1270.06</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F273" t="n">
-        <v>1</v>
+        <v>33911</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>5166.959999999999</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -8095,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -8108,12 +8108,12 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -8136,22 +8136,22 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>30.68</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F276" t="n">
-        <v>6</v>
+        <v>494</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -8164,22 +8164,22 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>62.87</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -8192,22 +8192,22 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -8220,50 +8220,50 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0</v>
+        <v>350.15</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F279" t="n">
+        <v>290</v>
+      </c>
+      <c r="G279" t="n">
+        <v>2668.64</v>
+      </c>
+      <c r="H279" t="n">
         <v>1</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-      <c r="H279" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F280" t="n">
-        <v>4</v>
+        <v>178</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8276,12 +8276,12 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(1)-Exact-SP</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -8291,7 +8291,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(11)-SP-Exact</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -8332,22 +8332,22 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>338.2</v>
       </c>
       <c r="E283" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F283" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -8360,12 +8360,12 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-SP-Exact</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -8375,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="F284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -8388,22 +8388,22 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW-Phrase-SP</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>40.45</v>
       </c>
       <c r="E285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F285" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
@@ -8416,12 +8416,12 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Cleaner/-B0F43P6D23-HG Exact(1)-SP</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="F286" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -8444,12 +8444,12 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -8472,40 +8472,40 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>6282.780000000001</v>
+        <v>0</v>
       </c>
       <c r="E288" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="F288" t="n">
-        <v>27576</v>
+        <v>14</v>
       </c>
       <c r="G288" t="n">
-        <v>42459.29</v>
+        <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexliv-Steam Mop Floor-B0DNJS23HS-BM-KW(1)-SP</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Nexlev-Steam Cleaner-B0F43P6D23-KW(3)-SP-Exact</t>
+          <t>Nexliv-steam cleaner for kitchen -KW(3)-BM-SP</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8537,13 +8537,13 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>104.33</v>
       </c>
       <c r="E290" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F290" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G290" t="n">
         <v>0</v>
@@ -8556,22 +8556,22 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexlive Steam Cleaner-B0F43P6D23-KW(1)BM-SP</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>16.74</v>
+        <v>18.77</v>
       </c>
       <c r="E291" t="n">
         <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G291" t="n">
         <v>0</v>
@@ -8584,22 +8584,22 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-BM-SP</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>154.83</v>
+        <v>911.54</v>
       </c>
       <c r="E292" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="F292" t="n">
-        <v>2636</v>
+        <v>10457</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -8612,22 +8612,22 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>23</v>
+        <v>457.8</v>
       </c>
       <c r="E293" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F293" t="n">
-        <v>1045</v>
+        <v>9060</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -8640,50 +8640,50 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>101.34</v>
+        <v>306.36</v>
       </c>
       <c r="E294" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F294" t="n">
-        <v>729</v>
+        <v>4099</v>
       </c>
       <c r="G294" t="n">
-        <v>2668.64</v>
+        <v>8048.309999999999</v>
       </c>
       <c r="H294" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexlive-Portable Cordless Lint Remover-B0FT8R24QM-Phrase-SP</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>657.84</v>
+        <v>21.96</v>
       </c>
       <c r="E295" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="F295" t="n">
-        <v>3933</v>
+        <v>658</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -8696,22 +8696,22 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Skadio B0BPPNQYX4-AT</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0BPPNQYX4</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>428.05</v>
+        <v>6</v>
       </c>
       <c r="E296" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F296" t="n">
-        <v>1464</v>
+        <v>114</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -8724,22 +8724,22 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>253.33</v>
+        <v>0</v>
       </c>
       <c r="E297" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>1437</v>
+        <v>15</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -8752,783 +8752,27 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>652.8</v>
+        <v>19.5</v>
       </c>
       <c r="E298" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="F298" t="n">
-        <v>13718</v>
+        <v>15</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr"/>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>B0DCK4DR1B</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>0</v>
-      </c>
-      <c r="E299" t="n">
-        <v>0</v>
-      </c>
-      <c r="F299" t="n">
-        <v>107</v>
-      </c>
-      <c r="G299" t="n">
-        <v>0</v>
-      </c>
-      <c r="H299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr"/>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="E300" t="n">
-        <v>5</v>
-      </c>
-      <c r="F300" t="n">
-        <v>117</v>
-      </c>
-      <c r="G300" t="n">
-        <v>0</v>
-      </c>
-      <c r="H300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr"/>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>B0DFCG2VGS</t>
-        </is>
-      </c>
-      <c r="D301" t="n">
-        <v>1270.06</v>
-      </c>
-      <c r="E301" t="n">
-        <v>132</v>
-      </c>
-      <c r="F301" t="n">
-        <v>33916</v>
-      </c>
-      <c r="G301" t="n">
-        <v>5166.959999999999</v>
-      </c>
-      <c r="H301" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr"/>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>B0D383WQPB</t>
-        </is>
-      </c>
-      <c r="D302" t="n">
-        <v>0</v>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-      <c r="F302" t="n">
-        <v>3</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr"/>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D303" t="n">
-        <v>0</v>
-      </c>
-      <c r="E303" t="n">
-        <v>0</v>
-      </c>
-      <c r="F303" t="n">
-        <v>105</v>
-      </c>
-      <c r="G303" t="n">
-        <v>0</v>
-      </c>
-      <c r="H303" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr"/>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D304" t="n">
-        <v>30.68</v>
-      </c>
-      <c r="E304" t="n">
-        <v>4</v>
-      </c>
-      <c r="F304" t="n">
-        <v>494</v>
-      </c>
-      <c r="G304" t="n">
-        <v>0</v>
-      </c>
-      <c r="H304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr"/>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
-        <v>62.87</v>
-      </c>
-      <c r="E305" t="n">
-        <v>6</v>
-      </c>
-      <c r="F305" t="n">
-        <v>435</v>
-      </c>
-      <c r="G305" t="n">
-        <v>0</v>
-      </c>
-      <c r="H305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr"/>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E306" t="n">
-        <v>1</v>
-      </c>
-      <c r="F306" t="n">
-        <v>13</v>
-      </c>
-      <c r="G306" t="n">
-        <v>0</v>
-      </c>
-      <c r="H306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr"/>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>350.15</v>
-      </c>
-      <c r="E307" t="n">
-        <v>35</v>
-      </c>
-      <c r="F307" t="n">
-        <v>290</v>
-      </c>
-      <c r="G307" t="n">
-        <v>2668.64</v>
-      </c>
-      <c r="H307" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr"/>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D308" t="n">
-        <v>262</v>
-      </c>
-      <c r="E308" t="n">
-        <v>20</v>
-      </c>
-      <c r="F308" t="n">
-        <v>178</v>
-      </c>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
-      <c r="H308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr"/>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(1)-Exact-SP</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D309" t="n">
-        <v>0</v>
-      </c>
-      <c r="E309" t="n">
-        <v>0</v>
-      </c>
-      <c r="F309" t="n">
-        <v>5</v>
-      </c>
-      <c r="G309" t="n">
-        <v>0</v>
-      </c>
-      <c r="H309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr"/>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(11)-SP-Exact</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D310" t="n">
-        <v>0</v>
-      </c>
-      <c r="E310" t="n">
-        <v>0</v>
-      </c>
-      <c r="F310" t="n">
-        <v>53</v>
-      </c>
-      <c r="G310" t="n">
-        <v>0</v>
-      </c>
-      <c r="H310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr"/>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D311" t="n">
-        <v>338.2</v>
-      </c>
-      <c r="E311" t="n">
-        <v>22</v>
-      </c>
-      <c r="F311" t="n">
-        <v>143</v>
-      </c>
-      <c r="G311" t="n">
-        <v>0</v>
-      </c>
-      <c r="H311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr"/>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-SP-Exact</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D312" t="n">
-        <v>0</v>
-      </c>
-      <c r="E312" t="n">
-        <v>0</v>
-      </c>
-      <c r="F312" t="n">
-        <v>2</v>
-      </c>
-      <c r="G312" t="n">
-        <v>0</v>
-      </c>
-      <c r="H312" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr"/>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D313" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="E313" t="n">
-        <v>2</v>
-      </c>
-      <c r="F313" t="n">
-        <v>47</v>
-      </c>
-      <c r="G313" t="n">
-        <v>0</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr"/>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Cleaner/-B0F43P6D23-HG Exact(1)-SP</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D314" t="n">
-        <v>0</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0</v>
-      </c>
-      <c r="F314" t="n">
-        <v>4</v>
-      </c>
-      <c r="G314" t="n">
-        <v>0</v>
-      </c>
-      <c r="H314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr"/>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D315" t="n">
-        <v>0</v>
-      </c>
-      <c r="E315" t="n">
-        <v>0</v>
-      </c>
-      <c r="F315" t="n">
-        <v>0</v>
-      </c>
-      <c r="G315" t="n">
-        <v>0</v>
-      </c>
-      <c r="H315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr"/>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D316" t="n">
-        <v>0</v>
-      </c>
-      <c r="E316" t="n">
-        <v>0</v>
-      </c>
-      <c r="F316" t="n">
-        <v>14</v>
-      </c>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
-      <c r="H316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr"/>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Nexliv-Steam Mop Floor-B0DNJS23HS-BM-KW(1)-SP</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D317" t="n">
-        <v>0</v>
-      </c>
-      <c r="E317" t="n">
-        <v>0</v>
-      </c>
-      <c r="F317" t="n">
-        <v>8</v>
-      </c>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
-      <c r="H317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr"/>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Nexliv-steam cleaner for kitchen -KW(3)-BM-SP</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D318" t="n">
-        <v>104.33</v>
-      </c>
-      <c r="E318" t="n">
-        <v>5</v>
-      </c>
-      <c r="F318" t="n">
-        <v>23</v>
-      </c>
-      <c r="G318" t="n">
-        <v>0</v>
-      </c>
-      <c r="H318" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr"/>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Nexlive Steam Cleaner-B0F43P6D23-KW(1)BM-SP</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D319" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="E319" t="n">
-        <v>1</v>
-      </c>
-      <c r="F319" t="n">
-        <v>7</v>
-      </c>
-      <c r="G319" t="n">
-        <v>0</v>
-      </c>
-      <c r="H319" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr"/>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-BM-SP</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D320" t="n">
-        <v>911.54</v>
-      </c>
-      <c r="E320" t="n">
-        <v>78</v>
-      </c>
-      <c r="F320" t="n">
-        <v>10457</v>
-      </c>
-      <c r="G320" t="n">
-        <v>0</v>
-      </c>
-      <c r="H320" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr"/>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D321" t="n">
-        <v>457.8</v>
-      </c>
-      <c r="E321" t="n">
-        <v>45</v>
-      </c>
-      <c r="F321" t="n">
-        <v>9060</v>
-      </c>
-      <c r="G321" t="n">
-        <v>0</v>
-      </c>
-      <c r="H321" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr"/>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Nexlive-Portable Cordless Lint Remover-B0FT8R24QM-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>B0FT8R24QM</t>
-        </is>
-      </c>
-      <c r="D322" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="E322" t="n">
-        <v>2</v>
-      </c>
-      <c r="F322" t="n">
-        <v>658</v>
-      </c>
-      <c r="G322" t="n">
-        <v>0</v>
-      </c>
-      <c r="H322" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr"/>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Skadio B0BPPNQYX4-AT</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>B0BPPNQYX4</t>
-        </is>
-      </c>
-      <c r="D323" t="n">
-        <v>6</v>
-      </c>
-      <c r="E323" t="n">
-        <v>1</v>
-      </c>
-      <c r="F323" t="n">
-        <v>114</v>
-      </c>
-      <c r="G323" t="n">
-        <v>0</v>
-      </c>
-      <c r="H323" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr"/>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
-      <c r="D324" t="n">
-        <v>0</v>
-      </c>
-      <c r="E324" t="n">
-        <v>0</v>
-      </c>
-      <c r="F324" t="n">
-        <v>15</v>
-      </c>
-      <c r="G324" t="n">
-        <v>0</v>
-      </c>
-      <c r="H324" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr"/>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D325" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E325" t="n">
-        <v>1</v>
-      </c>
-      <c r="F325" t="n">
-        <v>15</v>
-      </c>
-      <c r="G325" t="n">
-        <v>0</v>
-      </c>
-      <c r="H325" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10749,13 +9993,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>201.86</v>
+        <v>169.52</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
-        <v>4525</v>
+        <v>3718</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10777,13 +10021,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>716.5699999999999</v>
+        <v>536.71</v>
       </c>
       <c r="E44" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="F44" t="n">
-        <v>17267</v>
+        <v>12331</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10805,13 +10049,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>187.41</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2865</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10833,13 +10077,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>163.2</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2873</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -10861,13 +10105,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1401</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,46 +427,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -464,40 +476,40 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HnK_SP_KT_SS-01/SS-02 - Type A (Brand Analytic)</t>
+          <t>Campaign - 20/5/2026 16:32:01.948</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>306.36</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4099</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>8048.309999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HnK_SP_KT_VC-02</t>
+          <t>HnK_SP_KT_SS-01/SS-02 - Type A (Brand Analytic)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -520,12 +532,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_Auto_KM-01_B0DM66B2DW</t>
+          <t>HnK_SP_KT_VC-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -548,12 +560,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_CT_V-03_B0DQCWRG3H</t>
+          <t>HnK_SP_PT_SPM-01_B0DCK7J87D</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -576,12 +588,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_HSB-03_B0D9KFP4MG_MV_Exact</t>
+          <t>Nex_HPC_SP_Auto_KM-01_B0DM66B2DW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -604,12 +616,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_MV_Phrase &amp; Exact</t>
+          <t>Nex_HPC_SP_CT_FS-01_B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -632,7 +644,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_KT_V-03_Comp_B0DQCWRG3H_HV_Phrase &amp; Exact</t>
+          <t>Nex_HPC_SP_CT_V-03_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -660,12 +672,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
+          <t>Nex_HPC_SP_KT_BR-01_B0DKJXRXKM_BCG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -688,12 +700,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_(SM-01)_Wet &amp; Dry Mops</t>
+          <t>Nex_HPC_SP_KT_EA-01_B0D67727VG_Exact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -716,12 +728,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_CT_SC-01_B0CDPP45BM</t>
+          <t>Nex_HPC_SP_KT_HSB-03_B0D9KFP4MG_MV_Exact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -744,12 +756,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
+          <t>Nex_HPC_SP_KT_V-01_B0D83Q7L8W_BCG_Phrase_Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -772,12 +784,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_AP-04_B0GN8N96R5_Gen_Exact_HV</t>
+          <t>Nex_HPC_SP_KT_V-01_CVR_Exact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -800,12 +812,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_BCG</t>
+          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_CG_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -828,12 +840,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
+          <t>Nex_HPC_SP_KT_V-03_B0DQCWRG3H_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -856,12 +868,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_LR-02_B0D845B2DG_LV_Exact_Phrase</t>
+          <t>Nex_HPC_SP_KT_V-03_Comp_B0DQCWRG3H_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -884,12 +896,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
+          <t>Nex_HPC_SP_PT_CFM-01_B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -912,12 +924,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Gen_HV_Exact</t>
+          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -940,12 +952,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
+          <t>Nex_HnK_SP_Auto_MR-01_B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -968,12 +980,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
+          <t>Nex_HnK_SP_CT_(SM-01)_Wet &amp; Dry Mops</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -996,12 +1008,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP|SS-02-B0DNJP9T35| Auto</t>
+          <t>Nex_HnK_SP_CT_GS-02_B0CDPMX152</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1024,12 +1036,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_Auto_CAP-05_B0GN86G345</t>
+          <t>Nex_HnK_SP_CT_SC-01_B0CDPP45BM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1052,12 +1064,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT - MC-01</t>
+          <t>Nex_HnK_SP_Comp_PT_GS-02_B0CDPMX152</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1080,12 +1092,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
+          <t>Nex_HnK_SP_Comp_PT_HU-02_B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1108,22 +1120,22 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
+          <t>Nex_HnK_SP_Comp_PT_SC-01_B0CDPP45BM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>271.16</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>7727</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1136,124 +1148,124 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
+          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6277.82</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>23164</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>40350.82</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
+          <t>Nex_HnK_SP_KT_AP-04_B0GN8N96R5_Gen_Exact_HV</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1428.37</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>4681</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>11861.86</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
+          <t>Nex_HnK_SP_KT_CAP-05_B0GN86G345_Gen_HV_Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4123.32</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>5839</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>15504.22</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
+          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_CG_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2815.03</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>7391</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
+          <t>Nex_HnK_SP_KT_GS-02_B0CDPMX152_Gen_Phrase_HV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1276,7 +1288,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nex_HnK_SP_KT_GS-05_B0D383WQPB_Gen_HV_Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,59 +1297,59 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>314.3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2765</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3261.02</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev - B0D63FKYZ5 - Scalp Massager - Broad</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_BCG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>270.62</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>5297</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>951.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1360,50 +1372,50 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nex_HnK_SP_KT_LR-02_B0D845B2DG_LV_Exact_Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>227.09</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5913</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3542.35</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
+          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>655.96</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>13973</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,22 +1428,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
+          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_CG_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>319.49</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>6135</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,22 +1456,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
+          <t>Nex_HnK_SP_KT_MR-02_B0DCK7ZH5P_Gen_HV_Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>68.16</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>6864</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,22 +1484,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
+          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Adaptive Campaign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>228.14</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,50 +1512,50 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_Gen_HV_Exact</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1101.34</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>28946</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1295.76</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nex_HnK_SP_KT_SC-01_B0CDPP45BM_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>396.76</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2509</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,12 +1568,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1584,50 +1596,50 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2070.91</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>45952</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
+          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>741.49</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1495</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,22 +1652,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
+          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_CG_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>992.65</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>5076</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,22 +1680,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
+          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1202.93</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>22365</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,22 +1708,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
+          <t>Nex_HnK_SP|SS-02-B0DNJP9T35| Auto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1205.95</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>4696</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,19 +1736,19 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
+          <t>Nex_Hnk_SP_Auto_CAP-05_B0GN86G345</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1752,12 +1764,12 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Exact</t>
+          <t>Nex_Hnk_SP_KT - MC-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1780,22 +1792,22 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
+          <t>Nex_Hnk_SP_KT_ST-02_B0GN94YDY2_CG_MV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>195.84</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>6789</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,12 +1820,12 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - PT</t>
+          <t>Nex_Hnk_SP_PT - MC-01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1836,22 +1848,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
+          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1331.89</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>4791</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,208 +1876,208 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nex_Hnk_SP_PT_ST-03_B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1960.46</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>4018</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>14090.49</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
+          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>81.48</v>
+        <v>624.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="F53" t="n">
-        <v>3810</v>
+        <v>23360</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>668.64</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0CDPMX152 - Handheld Garment Steamer - KT - Comp - Multi Ad Group 07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2175.57</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>15844</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>10167.8</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1377.28</v>
+        <v>8823.559999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>78</v>
+        <v>594</v>
       </c>
       <c r="F55" t="n">
-        <v>9758</v>
+        <v>66936</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>59001.66</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1158.06</v>
+        <v>2340.72</v>
       </c>
       <c r="E56" t="n">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="F56" t="n">
-        <v>4427</v>
+        <v>10268</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>11861.86</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1314.32</v>
+        <v>6798.27</v>
       </c>
       <c r="E57" t="n">
-        <v>35</v>
+        <v>542</v>
       </c>
       <c r="F57" t="n">
-        <v>1049</v>
+        <v>8925</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>41895.72</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>869.6799999999999</v>
+        <v>3967.4</v>
       </c>
       <c r="E58" t="n">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="F58" t="n">
-        <v>25567</v>
+        <v>11214</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev - B0DQCWRG3H - Ionic 3 in 1 Hot Air Brush - Broad1</t>
+          <t>Nexlev - B0CYSLCRQS - Sofa &amp; Carpet Vacuum Cleaner - KT - Exact11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2088,68 +2100,68 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - BM</t>
+          <t>Nexlev - B0D25LNDSY - Rechargeable Electric Toothbrush 0 - SP - CT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>36.12</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>856.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0D383WQPB -  Foldable Garment Steamer - KT - Exact 07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1188.09</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>19938</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>15251.7</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC8NYY2 -  Ultrasonic Cool Mist Humidifier - KT - Excat 00</t>
+          <t>Nexlev - B0D383WQPB -  Foldable Garment Steamer 0 - SP - PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2172,22 +2184,22 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
+          <t>Nexlev - B0D383WQPB - Foldable Garment Steamer - SP - KT 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>279.27</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1813</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,22 +2212,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1131.54</v>
+        <v>421.85</v>
       </c>
       <c r="E64" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="F64" t="n">
-        <v>21399</v>
+        <v>23368</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2228,78 +2240,78 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2021.55</v>
+        <v>1195.74</v>
       </c>
       <c r="E65" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="F65" t="n">
-        <v>8384</v>
+        <v>8658</v>
       </c>
       <c r="G65" t="n">
-        <v>8005.92</v>
+        <v>4806.780000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
+          <t>Nexlev - B0D63FKYZ5 - Scalp Massager - Broad</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>543.34</v>
+        <v>412.45</v>
       </c>
       <c r="E66" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F66" t="n">
-        <v>2153</v>
+        <v>13128</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>951.4299999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>939.8</v>
+        <v>269.76</v>
       </c>
       <c r="E67" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F67" t="n">
-        <v>21222</v>
+        <v>4842</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,50 +2324,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6969.53</v>
+        <v>766.3199999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>344</v>
+        <v>56</v>
       </c>
       <c r="F68" t="n">
-        <v>33492</v>
+        <v>30535</v>
       </c>
       <c r="G68" t="n">
-        <v>23764.38</v>
+        <v>3542.35</v>
       </c>
       <c r="H68" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner 01 - KT - Branded - Phrase - Exact</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>742.64</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>15102</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,25 +2380,25 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2820.96</v>
+        <v>732.16</v>
       </c>
       <c r="E70" t="n">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="F70" t="n">
-        <v>87189</v>
+        <v>13186</v>
       </c>
       <c r="G70" t="n">
-        <v>6099.16</v>
+        <v>3120.33</v>
       </c>
       <c r="H70" t="n">
         <v>3</v>
@@ -2396,50 +2408,50 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1600.58</v>
+        <v>68.16</v>
       </c>
       <c r="E71" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="F71" t="n">
-        <v>23749</v>
+        <v>6864</v>
       </c>
       <c r="G71" t="n">
-        <v>6099.15</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>501.29</v>
+        <v>228.14</v>
       </c>
       <c r="E72" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>13053</v>
+        <v>374</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,50 +2464,50 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1369.94</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="F73" t="n">
-        <v>173</v>
+        <v>34143</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>4517.8</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7.3</v>
+        <v>396.76</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="F74" t="n">
-        <v>29</v>
+        <v>2509</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2508,12 +2520,12 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev - Stand Mixer - SP - CT</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2536,25 +2548,25 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4987.32</v>
+        <v>3295.94</v>
       </c>
       <c r="E76" t="n">
-        <v>210</v>
+        <v>447</v>
       </c>
       <c r="F76" t="n">
-        <v>12790</v>
+        <v>78254</v>
       </c>
       <c r="G76" t="n">
-        <v>9446.6</v>
+        <v>10680.51</v>
       </c>
       <c r="H76" t="n">
         <v>3</v>
@@ -2564,53 +2576,53 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>857.52</v>
+        <v>1666.15</v>
       </c>
       <c r="E77" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="F77" t="n">
-        <v>1961</v>
+        <v>8375</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>2826.27</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>956.04</v>
+        <v>1811.91</v>
       </c>
       <c r="E78" t="n">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="F78" t="n">
-        <v>4223</v>
+        <v>7856</v>
       </c>
       <c r="G78" t="n">
-        <v>338.14</v>
+        <v>2826.27</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -2620,106 +2632,106 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>822.23</v>
+        <v>1789.41</v>
       </c>
       <c r="E79" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F79" t="n">
-        <v>1771</v>
+        <v>27593</v>
       </c>
       <c r="G79" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>332.46</v>
+        <v>2042.25</v>
       </c>
       <c r="E80" t="n">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F80" t="n">
-        <v>1123</v>
+        <v>9655</v>
       </c>
       <c r="G80" t="n">
-        <v>619.49</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>642.13</v>
+        <v>415.13</v>
       </c>
       <c r="E81" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F81" t="n">
-        <v>1595</v>
+        <v>14087</v>
       </c>
       <c r="G81" t="n">
-        <v>1439.83</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Exact</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>899.73</v>
+        <v>217.96</v>
       </c>
       <c r="E82" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
-        <v>1489</v>
+        <v>6026</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2732,22 +2744,22 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>839.6</v>
+        <v>282.09</v>
       </c>
       <c r="E83" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F83" t="n">
-        <v>1076</v>
+        <v>11129</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2760,81 +2772,81 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - BM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6016.32</v>
+        <v>337.19</v>
       </c>
       <c r="E84" t="n">
-        <v>549</v>
+        <v>31</v>
       </c>
       <c r="F84" t="n">
-        <v>29894</v>
+        <v>9988</v>
       </c>
       <c r="G84" t="n">
-        <v>24060.14</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - Exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2289.71</v>
+        <v>52.68</v>
       </c>
       <c r="E85" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>2223</v>
+        <v>1079</v>
       </c>
       <c r="G85" t="n">
-        <v>8048.299999999999</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev - B0DKJSCLBD - Cordless Vacuum Cleaner - PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>120.93</v>
+        <v>1530.9</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="F86" t="n">
-        <v>920</v>
+        <v>4403</v>
       </c>
       <c r="G86" t="n">
-        <v>4236.44</v>
+        <v>1719.5</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
@@ -2844,22 +2856,22 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>116.57</v>
+        <v>2715.39</v>
       </c>
       <c r="E87" t="n">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="F87" t="n">
-        <v>2070</v>
+        <v>10496</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,50 +2884,50 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>114.04</v>
+        <v>4868.559999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="F88" t="n">
-        <v>725</v>
+        <v>15459</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>24997.14</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>155.63</v>
+        <v>231.41</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F89" t="n">
-        <v>3046</v>
+        <v>12895</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,106 +2940,106 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>552.41</v>
+        <v>3184.51</v>
       </c>
       <c r="E90" t="n">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="F90" t="n">
-        <v>20997</v>
+        <v>26860</v>
       </c>
       <c r="G90" t="n">
-        <v>1439.83</v>
+        <v>10167.8</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>154.54</v>
+        <v>2252.31</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="F91" t="n">
-        <v>498</v>
+        <v>16307</v>
       </c>
       <c r="G91" t="n">
-        <v>1270.34</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>94.27</v>
+        <v>1909.24</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="F92" t="n">
-        <v>1148</v>
+        <v>8590</v>
       </c>
       <c r="G92" t="n">
-        <v>1608.48</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5.86</v>
+        <v>2355.4</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="F93" t="n">
-        <v>62</v>
+        <v>1690</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,22 +3052,22 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>64.16</v>
+        <v>1889.78</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="F94" t="n">
-        <v>954</v>
+        <v>46990</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,50 +3080,50 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev - B0DQCWRG3H - Ionic 3 in 1 Hot Air Brush - Broad1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1618.44</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>5867</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1513.58</v>
+        <v>113.87</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F96" t="n">
-        <v>7597</v>
+        <v>15369</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,78 +3136,78 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - BM</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>178.43</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>2482</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1664.76</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>955.71</v>
+        <v>1886.07</v>
       </c>
       <c r="E98" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="F98" t="n">
-        <v>4014</v>
+        <v>31126</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>30333.9</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev - B0DVC8NYY2 -  Ultrasonic Cool Mist Humidifier - KT - Excat 00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>938.45</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>7355</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3208,22 +3220,22 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>880.5</v>
+        <v>858.0600000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F100" t="n">
-        <v>3413</v>
+        <v>3362</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,68 +3248,68 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>233.49</v>
+        <v>2404.45</v>
       </c>
       <c r="E101" t="n">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="F101" t="n">
-        <v>4224</v>
+        <v>46364</v>
       </c>
       <c r="G101" t="n">
-        <v>619.49</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>279.64</v>
+        <v>3434.88</v>
       </c>
       <c r="E102" t="n">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="F102" t="n">
-        <v>6301</v>
+        <v>16638</v>
       </c>
       <c r="G102" t="n">
-        <v>2932.21</v>
+        <v>13131.34</v>
       </c>
       <c r="H102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - KT - Comp - Multi Ad Group - 01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3307,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3320,22 +3332,22 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>13.39</v>
+        <v>1344.91</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="F104" t="n">
-        <v>372</v>
+        <v>4667</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3348,22 +3360,22 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>490.22</v>
+        <v>1948.47</v>
       </c>
       <c r="E105" t="n">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="F105" t="n">
-        <v>798</v>
+        <v>50589</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3376,190 +3388,190 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>126.67</v>
+        <v>10020.26</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>489</v>
       </c>
       <c r="F106" t="n">
-        <v>64</v>
+        <v>51390</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>35032.17</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner 01 - KT - Branded - Phrase - Exact</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>285.04</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>3462</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>1046.67</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>46.46</v>
+        <v>4419.89</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="F108" t="n">
-        <v>136</v>
+        <v>124692</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>10040.68</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev-B0D845B2DG-Lint Remover-SP-Auto</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>2508.02</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>37588</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>8132.21</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1390.99</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>40636</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1930.51</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0GN86G345 -  Car Air Purifier - KT - Multi Ad Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1410.3</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>22537</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>2879.66</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>431.85</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>8714</v>
+        <v>174</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3572,22 +3584,22 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>166.61</v>
+        <v>7.3</v>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>687</v>
+        <v>29</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3600,22 +3612,22 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev - Stand Mixer - SP - CT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>86.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,78 +3640,78 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev -B0CDPMX152- Garment Steamer -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1284.69</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>10440</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>7429.84</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>18605</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>12835.58</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>624.3299999999999</v>
+        <v>1492.55</v>
       </c>
       <c r="E117" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="F117" t="n">
-        <v>685</v>
+        <v>6924</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3712,109 +3724,109 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>494.03</v>
+        <v>1605.63</v>
       </c>
       <c r="E118" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F118" t="n">
-        <v>5086</v>
+        <v>8835</v>
       </c>
       <c r="G118" t="n">
-        <v>5351.43</v>
+        <v>338.14</v>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>639.71</v>
+        <v>1337.25</v>
       </c>
       <c r="E119" t="n">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="F119" t="n">
-        <v>1427</v>
+        <v>2726</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJP9T35-Spin Scrubber- SP -KT-Phrase</t>
+          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>627.4300000000001</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>3128</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1198.3</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2207.18</v>
+        <v>1211.04</v>
       </c>
       <c r="E121" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="F121" t="n">
-        <v>18507</v>
+        <v>3502</v>
       </c>
       <c r="G121" t="n">
-        <v>10167.8</v>
+        <v>2844.07</v>
       </c>
       <c r="H121" t="n">
         <v>2</v>
@@ -3824,35 +3836,35 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1035.69</v>
+        <v>1757.1</v>
       </c>
       <c r="E122" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>2051</v>
+        <v>2791</v>
       </c>
       <c r="G122" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3861,13 +3873,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>621.33</v>
+        <v>1529.19</v>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F123" t="n">
-        <v>817</v>
+        <v>1985</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3880,162 +3892,162 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1880.62</v>
+        <v>9810.969999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>63</v>
+        <v>910</v>
       </c>
       <c r="F124" t="n">
-        <v>3970</v>
+        <v>54038</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>52720.28</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>743.8</v>
+        <v>3718.11</v>
       </c>
       <c r="E125" t="n">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="F125" t="n">
-        <v>10894</v>
+        <v>3564</v>
       </c>
       <c r="G125" t="n">
-        <v>5209.32</v>
+        <v>13258.47</v>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1502.43</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>26778</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>5209.32</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>251.75</v>
+        <v>200.59</v>
       </c>
       <c r="E127" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="F127" t="n">
-        <v>12055</v>
+        <v>1728</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>6902.15</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>634.54</v>
+        <v>225.91</v>
       </c>
       <c r="E128" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>8412</v>
+        <v>3246</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>6608.48</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>406.53</v>
+        <v>179.2</v>
       </c>
       <c r="E129" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F129" t="n">
-        <v>2001</v>
+        <v>1461</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4048,109 +4060,109 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2729.26</v>
+        <v>340.14</v>
       </c>
       <c r="E130" t="n">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F130" t="n">
-        <v>5902</v>
+        <v>5966</v>
       </c>
       <c r="G130" t="n">
-        <v>9996.610000000001</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1459.35</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>41248</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>5557.62</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>154.98</v>
+        <v>398.55</v>
       </c>
       <c r="E132" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F132" t="n">
-        <v>1040</v>
+        <v>1256</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1270.34</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3779.3</v>
+        <v>293.15</v>
       </c>
       <c r="E133" t="n">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="F133" t="n">
-        <v>10460</v>
+        <v>3121</v>
       </c>
       <c r="G133" t="n">
-        <v>14106.77</v>
+        <v>5289.84</v>
       </c>
       <c r="H133" t="n">
         <v>4</v>
@@ -4160,124 +4172,124 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3355.44</v>
+        <v>5.86</v>
       </c>
       <c r="E134" t="n">
-        <v>260</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>129842</v>
+        <v>62</v>
       </c>
       <c r="G134" t="n">
-        <v>12198.3</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0CDPMX152-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>156.96</v>
+        <v>81.67999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F135" t="n">
-        <v>9789</v>
+        <v>1163</v>
       </c>
       <c r="G135" t="n">
-        <v>4066.1</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>3530.36</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="F136" t="n">
-        <v>48</v>
+        <v>12324</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>159.42</v>
+        <v>2893.86</v>
       </c>
       <c r="E137" t="n">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="F137" t="n">
-        <v>3625</v>
+        <v>18457</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -4287,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4300,50 +4312,50 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>40.87</v>
+        <v>1459.46</v>
       </c>
       <c r="E139" t="n">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="F139" t="n">
-        <v>3311</v>
+        <v>6979</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>2456.78</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>19.31</v>
+        <v>1676.43</v>
       </c>
       <c r="E140" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="F140" t="n">
-        <v>2343</v>
+        <v>11610</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4356,12 +4368,12 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4371,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4384,134 +4396,134 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1752.66</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F142" t="n">
-        <v>23</v>
+        <v>8554</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>2367.8</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>13.2</v>
+        <v>593.05</v>
       </c>
       <c r="E143" t="n">
+        <v>49</v>
+      </c>
+      <c r="F143" t="n">
+        <v>8346</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1238.98</v>
+      </c>
+      <c r="H143" t="n">
         <v>2</v>
-      </c>
-      <c r="F143" t="n">
-        <v>1144</v>
-      </c>
-      <c r="G143" t="n">
-        <v>677.12</v>
-      </c>
-      <c r="H143" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6.69</v>
+        <v>697.46</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="F144" t="n">
-        <v>42</v>
+        <v>13360</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>3551.7</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.2</v>
+        <v>263.23</v>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F145" t="n">
-        <v>80</v>
+        <v>5916</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>3197.46</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>18</v>
+        <v>607</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4524,50 +4536,50 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>14.9</v>
+        <v>2736.15</v>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="F147" t="n">
-        <v>86</v>
+        <v>8612</v>
       </c>
       <c r="G147" t="n">
-        <v>1295.76</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>21.14</v>
+        <v>324.43</v>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F148" t="n">
-        <v>1159</v>
+        <v>332</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4580,50 +4592,50 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>13.33</v>
+        <v>563.36</v>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F149" t="n">
-        <v>51</v>
+        <v>5985</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>2093.34</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>57.27</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4636,12 +4648,12 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-Auto</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -4651,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4664,22 +4676,22 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>13.6</v>
+        <v>43.25</v>
       </c>
       <c r="E152" t="n">
         <v>2</v>
       </c>
       <c r="F152" t="n">
-        <v>479</v>
+        <v>300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4692,50 +4704,50 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6.8</v>
+        <v>2284.46</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="F153" t="n">
-        <v>366</v>
+        <v>37700</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4312.71</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>30.89</v>
+        <v>882.48</v>
       </c>
       <c r="E154" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F154" t="n">
-        <v>496</v>
+        <v>13208</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4748,50 +4760,50 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>58.25</v>
+        <v>797.0700000000001</v>
       </c>
       <c r="E155" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="F155" t="n">
-        <v>354</v>
+        <v>5318</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>2152.54</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6.22</v>
+        <v>219.1</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F156" t="n">
-        <v>243</v>
+        <v>997</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4804,50 +4816,50 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>31.38</v>
+        <v>1994.26</v>
       </c>
       <c r="E157" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="F157" t="n">
-        <v>805</v>
+        <v>12943</v>
       </c>
       <c r="G157" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4860,22 +4872,22 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1378.36</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F159" t="n">
-        <v>4</v>
+        <v>1558</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4888,78 +4900,78 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6.8</v>
+        <v>1039.08</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="F160" t="n">
+        <v>9253</v>
+      </c>
+      <c r="G160" t="n">
+        <v>11320</v>
+      </c>
+      <c r="H160" t="n">
         <v>6</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1805.51</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F161" t="n">
-        <v>5</v>
+        <v>3894</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>2665.71</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJP9T35-Spin Scrubber- SP -KT-Phrase</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>21.89</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4972,78 +4984,78 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>107.07</v>
+        <v>4005.18</v>
       </c>
       <c r="E163" t="n">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="F163" t="n">
-        <v>2509</v>
+        <v>36978</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>22028.81</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>9.33</v>
+        <v>1384.58</v>
       </c>
       <c r="E164" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="F164" t="n">
-        <v>229</v>
+        <v>3538</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>850.4</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F165" t="n">
-        <v>82</v>
+        <v>2244</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5056,162 +5068,162 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>3397.64</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F166" t="n">
-        <v>5</v>
+        <v>10649</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>3388.98</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>13.6</v>
+        <v>1605.81</v>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="F167" t="n">
-        <v>59</v>
+        <v>23362</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>5209.32</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>6.19</v>
+        <v>2434.87</v>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="F168" t="n">
-        <v>45</v>
+        <v>47320</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>8044.07</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>17.74</v>
+        <v>338.94</v>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F169" t="n">
-        <v>770</v>
+        <v>17514</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>4914.4</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>2047.91</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>28906</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>10013.56</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>532.4</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F171" t="n">
-        <v>31</v>
+        <v>3634</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5224,50 +5236,50 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>4598.99</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="F172" t="n">
-        <v>26</v>
+        <v>11679</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>9657.620000000001</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>25.45</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5280,134 +5292,134 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>6.78</v>
+        <v>414.03</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F174" t="n">
-        <v>3494</v>
+        <v>1751</v>
       </c>
       <c r="G174" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4.79</v>
+        <v>7188.77</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c r="F175" t="n">
-        <v>512</v>
+        <v>21714</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>32872.04</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>14.49</v>
+        <v>4832.73</v>
       </c>
       <c r="E176" t="n">
-        <v>3</v>
+        <v>368</v>
       </c>
       <c r="F176" t="n">
-        <v>296</v>
+        <v>183566</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>16139.83</v>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>302.16</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F177" t="n">
-        <v>65</v>
+        <v>19040</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>6099.15</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>592.27</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F178" t="n">
-        <v>94</v>
+        <v>5436</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5420,22 +5432,22 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.31</v>
+        <v>506.68</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F179" t="n">
-        <v>70</v>
+        <v>6898</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5453,17 +5465,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>565</v>
+        <v>7</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5481,17 +5493,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>40.87</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F181" t="n">
-        <v>200</v>
+        <v>3311</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5509,17 +5521,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>14.93</v>
+        <v>19.31</v>
       </c>
       <c r="E182" t="n">
         <v>3</v>
       </c>
       <c r="F182" t="n">
-        <v>2303</v>
+        <v>2343</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5537,7 +5549,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -5547,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5565,7 +5577,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -5575,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5593,23 +5605,23 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>6.8</v>
+        <v>13.2</v>
       </c>
       <c r="E185" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1144</v>
+      </c>
+      <c r="G185" t="n">
+        <v>677.12</v>
+      </c>
+      <c r="H185" t="n">
         <v>1</v>
-      </c>
-      <c r="F185" t="n">
-        <v>282</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -5621,17 +5633,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>13.5</v>
+        <v>6.69</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5649,17 +5661,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5677,17 +5689,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>13.47</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>1509</v>
+        <v>18</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5705,45 +5717,45 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>75.95</v>
+        <v>14.9</v>
       </c>
       <c r="E189" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F189" t="n">
-        <v>791</v>
+        <v>86</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1295.76</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>21.14</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F190" t="n">
-        <v>19</v>
+        <v>1159</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5756,22 +5768,22 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F191" t="n">
-        <v>551</v>
+        <v>51</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5784,22 +5796,22 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>973</v>
+        <v>61</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5812,12 +5824,12 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -5827,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5840,22 +5852,22 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" t="n">
-        <v>3005</v>
+        <v>479</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5868,22 +5880,22 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>6.68</v>
+        <v>6.8</v>
       </c>
       <c r="E195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>883</v>
+        <v>366</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5896,22 +5908,22 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1.57</v>
+        <v>30.89</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F196" t="n">
-        <v>314</v>
+        <v>496</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5924,22 +5936,22 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>58.25</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F197" t="n">
-        <v>108</v>
+        <v>354</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5952,22 +5964,22 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>8.92</v>
+        <v>6.22</v>
       </c>
       <c r="E198" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F198" t="n">
-        <v>410</v>
+        <v>243</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5980,50 +5992,50 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1.3</v>
+        <v>31.38</v>
       </c>
       <c r="E199" t="n">
+        <v>6</v>
+      </c>
+      <c r="F199" t="n">
+        <v>805</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="H199" t="n">
         <v>1</v>
-      </c>
-      <c r="F199" t="n">
-        <v>672</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>8.6</v>
+        <v>40.5</v>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F200" t="n">
-        <v>578</v>
+        <v>444</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -6036,12 +6048,12 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -6051,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>4764</v>
+        <v>4</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6064,22 +6076,22 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>306</v>
+        <v>6</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -6092,22 +6104,22 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>392</v>
+        <v>5</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6120,22 +6132,22 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>11.3</v>
+        <v>21.89</v>
       </c>
       <c r="E204" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F204" t="n">
-        <v>618</v>
+        <v>48</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6148,22 +6160,22 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>7.69</v>
+        <v>107.07</v>
       </c>
       <c r="E205" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F205" t="n">
-        <v>143</v>
+        <v>2509</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6176,22 +6188,22 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>9.33</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F206" t="n">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6204,22 +6216,22 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6232,12 +6244,12 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -6247,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6260,22 +6272,22 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>347.92</v>
+        <v>13.6</v>
       </c>
       <c r="E209" t="n">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="F209" t="n">
-        <v>12545</v>
+        <v>59</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6288,50 +6300,50 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>465.05</v>
+        <v>6.19</v>
       </c>
       <c r="E210" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>18384</v>
+        <v>45</v>
       </c>
       <c r="G210" t="n">
-        <v>1944.07</v>
+        <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1.3</v>
+        <v>17.74</v>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F211" t="n">
-        <v>259</v>
+        <v>770</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6344,22 +6356,22 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>14.85</v>
+        <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>1843</v>
+        <v>4</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6372,12 +6384,12 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -6387,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>284</v>
+        <v>31</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6400,22 +6412,22 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>50.64</v>
+        <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>2487</v>
+        <v>26</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6428,22 +6440,22 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>9</v>
+        <v>25.45</v>
       </c>
       <c r="E215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F215" t="n">
-        <v>601</v>
+        <v>194</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6456,50 +6468,50 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>11.3</v>
+        <v>6.78</v>
       </c>
       <c r="E216" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>431</v>
+        <v>3494</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>2668.64</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>46</v>
+        <v>512</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6512,22 +6524,22 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>14.49</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F218" t="n">
-        <v>3</v>
+        <v>296</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6540,22 +6552,22 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>496</v>
+        <v>65</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6568,12 +6580,12 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -6583,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>530</v>
+        <v>94</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6596,22 +6608,22 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>2.3</v>
+        <v>5.31</v>
       </c>
       <c r="E221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>1481</v>
+        <v>70</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6624,22 +6636,22 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F222" t="n">
-        <v>2</v>
+        <v>565</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6652,22 +6664,22 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>2938</v>
+        <v>200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6680,22 +6692,22 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
+        <v>14.93</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F224" t="n">
-        <v>10</v>
+        <v>2303</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6708,22 +6720,22 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6736,22 +6748,22 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="E226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>975</v>
+        <v>129</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6764,22 +6776,22 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.63</v>
+        <v>6.8</v>
       </c>
       <c r="E227" t="n">
         <v>1</v>
       </c>
       <c r="F227" t="n">
-        <v>151</v>
+        <v>282</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6792,22 +6804,22 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1.29</v>
+        <v>13.5</v>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F228" t="n">
-        <v>375</v>
+        <v>115</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6820,12 +6832,12 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -6835,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6848,50 +6860,50 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>5.800000000000001</v>
+        <v>13.47</v>
       </c>
       <c r="E230" t="n">
         <v>2</v>
       </c>
       <c r="F230" t="n">
-        <v>43</v>
+        <v>1509</v>
       </c>
       <c r="G230" t="n">
-        <v>211.02</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>5.33</v>
+        <v>75.95</v>
       </c>
       <c r="E231" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F231" t="n">
-        <v>184</v>
+        <v>791</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6909,23 +6921,23 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>49.46</v>
+        <v>0</v>
       </c>
       <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
         <v>19</v>
       </c>
-      <c r="F232" t="n">
-        <v>592</v>
-      </c>
       <c r="G232" t="n">
-        <v>211.02</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -6937,17 +6949,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="E233" t="n">
         <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>31</v>
+        <v>552</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6965,17 +6977,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>24.87</v>
+        <v>1</v>
       </c>
       <c r="E234" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F234" t="n">
-        <v>3218</v>
+        <v>973</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6993,7 +7005,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -7003,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7021,17 +7033,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F236" t="n">
-        <v>403</v>
+        <v>3005</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7049,17 +7061,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>11.79</v>
+        <v>6.68</v>
       </c>
       <c r="E237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F237" t="n">
-        <v>1133</v>
+        <v>884</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7077,17 +7089,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="E238" t="n">
         <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -7105,17 +7117,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>8.07</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>537</v>
+        <v>108</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7133,17 +7145,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>4.3</v>
+        <v>8.92</v>
       </c>
       <c r="E240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F240" t="n">
-        <v>1271</v>
+        <v>410</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7161,17 +7173,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>18.88</v>
+        <v>1.3</v>
       </c>
       <c r="E241" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F241" t="n">
-        <v>383</v>
+        <v>673</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7184,22 +7196,22 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -7212,12 +7224,12 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -7227,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>1</v>
+        <v>4764</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7240,22 +7252,22 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>5</v>
+        <v>307</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7268,22 +7280,22 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7296,22 +7308,22 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>1</v>
+        <v>622</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -7324,22 +7336,22 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F247" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7352,7 +7364,7 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7367,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -7380,22 +7392,22 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -7408,12 +7420,12 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -7423,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -7436,22 +7448,22 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0</v>
+        <v>348.92</v>
       </c>
       <c r="E251" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>12556</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7464,50 +7476,50 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>465.05</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="F252" t="n">
-        <v>4</v>
+        <v>18404</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>1944.07</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7520,22 +7532,22 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0</v>
+        <v>14.85</v>
       </c>
       <c r="E254" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>1843</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7548,12 +7560,12 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -7563,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7576,22 +7588,22 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0</v>
+        <v>50.64</v>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>2487</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7604,22 +7616,22 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F257" t="n">
-        <v>3</v>
+        <v>601</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -7632,22 +7644,22 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F258" t="n">
-        <v>1</v>
+        <v>432</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -7660,12 +7672,12 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -7675,7 +7687,7 @@
         <v>0</v>
       </c>
       <c r="F259" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -7688,50 +7700,50 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4406.93</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
-        <v>412</v>
+        <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>15600</v>
+        <v>3</v>
       </c>
       <c r="G260" t="n">
-        <v>23977.1</v>
+        <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>17</v>
+        <v>496</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -7744,12 +7756,12 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Nexlev-Steam Cleaner-B0F43P6D23-KW(3)-SP-Exact</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -7759,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="F262" t="n">
-        <v>4</v>
+        <v>530</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7772,22 +7784,22 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>16.74</v>
+        <v>2.3</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F263" t="n">
-        <v>18</v>
+        <v>1481</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -7800,22 +7812,22 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>154.83</v>
+        <v>0</v>
       </c>
       <c r="E264" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>2636</v>
+        <v>2</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -7828,22 +7840,22 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>23</v>
+        <v>2.6</v>
       </c>
       <c r="E265" t="n">
         <v>2</v>
       </c>
       <c r="F265" t="n">
-        <v>1045</v>
+        <v>2938</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -7856,50 +7868,50 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>101.34</v>
+        <v>0</v>
       </c>
       <c r="E266" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F266" t="n">
-        <v>729</v>
+        <v>10</v>
       </c>
       <c r="G266" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>657.84</v>
+        <v>1.33</v>
       </c>
       <c r="E267" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="F267" t="n">
-        <v>3933</v>
+        <v>28</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -7912,22 +7924,22 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>428.05</v>
+        <v>5.08</v>
       </c>
       <c r="E268" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F268" t="n">
-        <v>1464</v>
+        <v>975</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -7940,22 +7952,22 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>253.33</v>
+        <v>1.63</v>
       </c>
       <c r="E269" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F269" t="n">
-        <v>1437</v>
+        <v>151</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -7968,22 +7980,22 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>652.8</v>
+        <v>1.29</v>
       </c>
       <c r="E270" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>13715</v>
+        <v>375</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -7996,12 +8008,12 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -8011,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -8024,106 +8036,106 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>58.79</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="E272" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F272" t="n">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>211.02</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1270.06</v>
+        <v>5.33</v>
       </c>
       <c r="E273" t="n">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="F273" t="n">
-        <v>33911</v>
+        <v>184</v>
       </c>
       <c r="G273" t="n">
-        <v>5166.959999999999</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>49.46</v>
       </c>
       <c r="E274" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>592</v>
       </c>
       <c r="G274" t="n">
-        <v>0</v>
+        <v>211.02</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -8136,22 +8148,22 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>30.68</v>
+        <v>24.87</v>
       </c>
       <c r="E276" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F276" t="n">
-        <v>494</v>
+        <v>3218</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -8164,22 +8176,22 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>62.87</v>
+        <v>0</v>
       </c>
       <c r="E277" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -8192,22 +8204,22 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>21.4</v>
+        <v>6</v>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F278" t="n">
-        <v>13</v>
+        <v>403</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -8220,50 +8232,50 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>350.15</v>
+        <v>11.79</v>
       </c>
       <c r="E279" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F279" t="n">
-        <v>290</v>
+        <v>1134</v>
       </c>
       <c r="G279" t="n">
-        <v>2668.64</v>
+        <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>262</v>
+        <v>3</v>
       </c>
       <c r="E280" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F280" t="n">
-        <v>178</v>
+        <v>363</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8276,22 +8288,22 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(1)-Exact-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>8.07</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F281" t="n">
-        <v>5</v>
+        <v>537</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -8304,22 +8316,22 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(11)-SP-Exact</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>53</v>
+        <v>1271</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -8332,22 +8344,22 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>338.2</v>
+        <v>18.88</v>
       </c>
       <c r="E283" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F283" t="n">
-        <v>143</v>
+        <v>383</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -8360,12 +8372,12 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-SP-Exact</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -8375,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="F284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -8388,22 +8400,22 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW-Phrase-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>40.45</v>
+        <v>0</v>
       </c>
       <c r="E285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F285" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
@@ -8416,22 +8428,22 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner/-B0F43P6D23-HG Exact(1)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -8444,12 +8456,12 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -8459,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -8472,12 +8484,12 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -8487,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="F288" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G288" t="n">
         <v>0</v>
@@ -8500,12 +8512,12 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor-B0DNJS23HS-BM-KW(1)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -8515,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -8528,22 +8540,22 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Nexliv-steam cleaner for kitchen -KW(3)-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>104.33</v>
+        <v>0</v>
       </c>
       <c r="E290" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F290" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G290" t="n">
         <v>0</v>
@@ -8556,22 +8568,22 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nexlive Steam Cleaner-B0F43P6D23-KW(1)BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>18.77</v>
+        <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F291" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G291" t="n">
         <v>0</v>
@@ -8584,22 +8596,22 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>911.54</v>
+        <v>0</v>
       </c>
       <c r="E292" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F292" t="n">
-        <v>10457</v>
+        <v>1</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -8612,22 +8624,22 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>457.8</v>
+        <v>0</v>
       </c>
       <c r="E293" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>9060</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -8640,50 +8652,50 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>306.36</v>
+        <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F294" t="n">
-        <v>4099</v>
+        <v>4</v>
       </c>
       <c r="G294" t="n">
-        <v>8048.309999999999</v>
+        <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nexlive-Portable Cordless Lint Remover-B0FT8R24QM-Phrase-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>21.96</v>
+        <v>0</v>
       </c>
       <c r="E295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>658</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -8696,22 +8708,22 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Skadio B0BPPNQYX4-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>B0BPPNQYX4</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F296" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -8724,12 +8736,12 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -8739,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -8752,27 +8764,1175 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>B0F678L8YT</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>B0F67BSF2R</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="n">
+        <v>3</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>B0FJG5PFGQ</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" t="n">
+        <v>2</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>6883.79</v>
+      </c>
+      <c r="E302" t="n">
+        <v>555</v>
+      </c>
+      <c r="F302" t="n">
+        <v>30755</v>
+      </c>
+      <c r="G302" t="n">
+        <v>42459.29</v>
+      </c>
+      <c r="H302" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" t="n">
+        <v>17</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Nexlev-Steam Cleaner-B0F43P6D23-KW(3)-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" t="n">
+        <v>4</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1</v>
+      </c>
+      <c r="F305" t="n">
+        <v>18</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>B0D9KFP4MG</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>154.83</v>
+      </c>
+      <c r="E306" t="n">
+        <v>16</v>
+      </c>
+      <c r="F306" t="n">
+        <v>2636</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>B0D9KFP4MG</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>23</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1045</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="E308" t="n">
+        <v>12</v>
+      </c>
+      <c r="F308" t="n">
+        <v>729</v>
+      </c>
+      <c r="G308" t="n">
+        <v>2668.64</v>
+      </c>
+      <c r="H308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>657.84</v>
+      </c>
+      <c r="E309" t="n">
+        <v>58</v>
+      </c>
+      <c r="F309" t="n">
+        <v>3933</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>428.05</v>
+      </c>
+      <c r="E310" t="n">
+        <v>27</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>253.33</v>
+      </c>
+      <c r="E311" t="n">
+        <v>21</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1437</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>652.8</v>
+      </c>
+      <c r="E312" t="n">
+        <v>69</v>
+      </c>
+      <c r="F312" t="n">
+        <v>13719</v>
+      </c>
+      <c r="G312" t="n">
+        <v>0</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>B0DCK4DR1B</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" t="n">
+        <v>107</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="E314" t="n">
+        <v>5</v>
+      </c>
+      <c r="F314" t="n">
+        <v>117</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1270.06</v>
+      </c>
+      <c r="E315" t="n">
+        <v>132</v>
+      </c>
+      <c r="F315" t="n">
+        <v>33917</v>
+      </c>
+      <c r="G315" t="n">
+        <v>5166.959999999999</v>
+      </c>
+      <c r="H315" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+      <c r="F316" t="n">
+        <v>3</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" t="n">
+        <v>105</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="E318" t="n">
+        <v>4</v>
+      </c>
+      <c r="F318" t="n">
+        <v>494</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="E319" t="n">
+        <v>6</v>
+      </c>
+      <c r="F319" t="n">
+        <v>435</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1</v>
+      </c>
+      <c r="F320" t="n">
+        <v>13</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="E321" t="n">
+        <v>35</v>
+      </c>
+      <c r="F321" t="n">
+        <v>290</v>
+      </c>
+      <c r="G321" t="n">
+        <v>2668.64</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>262</v>
+      </c>
+      <c r="E322" t="n">
+        <v>20</v>
+      </c>
+      <c r="F322" t="n">
+        <v>178</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(1)-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" t="n">
+        <v>5</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(11)-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" t="n">
+        <v>53</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="E325" t="n">
+        <v>22</v>
+      </c>
+      <c r="F325" t="n">
+        <v>143</v>
+      </c>
+      <c r="G325" t="n">
+        <v>0</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" t="n">
+        <v>2</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="E327" t="n">
+        <v>2</v>
+      </c>
+      <c r="F327" t="n">
+        <v>47</v>
+      </c>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner/-B0F43P6D23-HG Exact(1)-SP</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
+      <c r="F328" t="n">
+        <v>4</v>
+      </c>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>0</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" t="n">
+        <v>14</v>
+      </c>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor-B0DNJS23HS-BM-KW(1)-SP</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" t="n">
+        <v>8</v>
+      </c>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Nexliv-steam cleaner for kitchen -KW(3)-BM-SP</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="E332" t="n">
+        <v>5</v>
+      </c>
+      <c r="F332" t="n">
+        <v>23</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Nexlive Steam Cleaner-B0F43P6D23-KW(1)BM-SP</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+      <c r="F333" t="n">
+        <v>7</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-BM-SP</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>911.54</v>
+      </c>
+      <c r="E334" t="n">
+        <v>78</v>
+      </c>
+      <c r="F334" t="n">
+        <v>10457</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="E335" t="n">
+        <v>45</v>
+      </c>
+      <c r="F335" t="n">
+        <v>9062</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Nexlive-Portable Cordless Lint Remover-B0FT8R24QM-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>B0FT8R24QM</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="E336" t="n">
+        <v>2</v>
+      </c>
+      <c r="F336" t="n">
+        <v>658</v>
+      </c>
+      <c r="G336" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Skadio B0BPPNQYX4-AT</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>B0BPPNQYX4</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>6</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+      <c r="F337" t="n">
+        <v>114</v>
+      </c>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" t="n">
+        <v>15</v>
+      </c>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+      <c r="H338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
           <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C339" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D298" t="n">
+      <c r="D339" t="n">
         <v>19.5</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E339" t="n">
         <v>1</v>
       </c>
-      <c r="F298" t="n">
+      <c r="F339" t="n">
         <v>15</v>
       </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
-      <c r="H298" t="n">
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8791,42 +9951,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -9993,13 +11153,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>169.52</v>
+        <v>268.68</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>3718</v>
+        <v>4835</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10021,13 +11181,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>536.71</v>
+        <v>813.3099999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="F44" t="n">
-        <v>12331</v>
+        <v>19593</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10049,13 +11209,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>230.65</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>4010</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10077,13 +11237,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>249.83</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>3612</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -10105,13 +11265,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>66.09</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1725</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10331,47 +11491,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -9951,42 +9939,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -11491,47 +11479,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -9939,42 +9951,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -11479,47 +11491,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -9951,42 +9939,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -11491,47 +11479,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week21.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -9939,42 +9951,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -11479,47 +11491,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
